--- a/Data/Data-sheet.xlsx
+++ b/Data/Data-sheet.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tristancools/Documents/Arduino/Project-experimenteren2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0C430F3-B25A-804D-81B1-C60D6C07B538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{574319FD-C77A-C747-B259-37068857164B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Kalibratie" sheetId="1" r:id="rId1"/>
-    <sheet name="Metingen" sheetId="3" r:id="rId2"/>
-    <sheet name="Verwerking" sheetId="2" r:id="rId3"/>
+    <sheet name="Metingen" sheetId="2" r:id="rId2"/>
+    <sheet name="Verwerking" sheetId="3" r:id="rId3"/>
+    <sheet name="Verwerking_2" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="54">
   <si>
     <t>d(cm)</t>
   </si>
@@ -82,28 +86,23 @@
     <t>V_AMPLIT (V)</t>
   </si>
   <si>
-    <t>Meting:</t>
+    <t>Constantes:</t>
   </si>
   <si>
-    <t>Set 1</t>
-  </si>
-  <si>
-    <t>Set  2</t>
-  </si>
-  <si>
-    <t>Set 3</t>
-  </si>
-  <si>
-    <t>Set 4</t>
-  </si>
-  <si>
-    <t>Set 5</t>
+    <t>Meting:</t>
   </si>
   <si>
     <t>Delta V_AC (V)</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">V_piek = (Delta V_AC)_rms </t>
     </r>
     <r>
@@ -111,6 +110,7 @@
         <sz val="5"/>
         <color theme="1"/>
         <rFont val="Calibri (Body)"/>
+        <charset val="1"/>
       </rPr>
       <t>want lockin meet rms</t>
     </r>
@@ -120,13 +120,23 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> (V)</t>
     </r>
   </si>
   <si>
+    <t>V_CD = V_AVG (V)</t>
+  </si>
+  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t>Draaihoek (radialen)</t>
     </r>
     <r>
@@ -134,18 +144,40 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Calibri (Body)"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> (=Delta(V_AC)/(2V_DC)) </t>
     </r>
   </si>
   <si>
-    <t>lengte kwarts (mm)</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>Draaihoek (graden)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (=Delta(V_AC)/(2V_DC)) </t>
+    </r>
   </si>
   <si>
-    <t>AF(lengte) (mm)</t>
+    <t>schalingsfactor: I/(I_ref)</t>
   </si>
   <si>
-    <t>B_veld door staaf (T*m)</t>
+    <t>B_spoel (mT)</t>
+  </si>
+  <si>
+    <t>B_spoel (T)</t>
   </si>
   <si>
     <t>Verdet-cste V (rad/Tm)</t>
@@ -154,47 +186,85 @@
     <t>Verdet (graden/(T*m))</t>
   </si>
   <si>
-    <r>
-      <t>Draaihoek (graden)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t xml:space="preserve"> (=Delta(V_AC)/(2V_DC)) </t>
-    </r>
+    <t>Set 1</t>
   </si>
   <si>
-    <t>V_CD = V_AVG (V)</t>
+    <t>I_referentie (mA)</t>
+  </si>
+  <si>
+    <t>lengte kwarts (mm)</t>
+  </si>
+  <si>
+    <t>Set  2</t>
+  </si>
+  <si>
+    <t>lengte kwarts (m)</t>
+  </si>
+  <si>
+    <t>AF(lengte) (mm)</t>
+  </si>
+  <si>
+    <t>Set 3</t>
   </si>
   <si>
     <t>B_referentie (mT) zie interpolatie python</t>
   </si>
   <si>
-    <t>Constantes:</t>
+    <t>Set 4</t>
   </si>
   <si>
     <t>B_referentie door staaf  (T*mm)</t>
   </si>
   <si>
-    <t>B_spoel (T)</t>
+    <t>B_veld door staaf (T*m)</t>
   </si>
   <si>
-    <t>B_spoel (mT)</t>
-  </si>
-  <si>
-    <t>lengte kwarts (m)</t>
-  </si>
-  <si>
-    <t>schalingsfactor: I/(I_ref)</t>
-  </si>
-  <si>
-    <t>I_referentie (mA)</t>
+    <t>Set 5</t>
   </si>
   <si>
     <t>Golflengte laser (nm)</t>
+  </si>
+  <si>
+    <t>C² 1</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>C²2</t>
+  </si>
+  <si>
+    <t>theta1</t>
+  </si>
+  <si>
+    <t>theta2</t>
+  </si>
+  <si>
+    <t>dtheta</t>
+  </si>
+  <si>
+    <t>Verdet (rad/(T * mm))</t>
+  </si>
+  <si>
+    <t>AF voltages (gok)</t>
+  </si>
+  <si>
+    <t>AF_Verdet</t>
+  </si>
+  <si>
+    <t>AF_I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AF_B </t>
+  </si>
+  <si>
+    <t>AF_B (mt)</t>
+  </si>
+  <si>
+    <t>RF_Verdet</t>
+  </si>
+  <si>
+    <t>Foutpercentage</t>
   </si>
 </sst>
 </file>
@@ -207,23 +277,26 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="5"/>
+      <color theme="1"/>
+      <name val="Calibri (Body)"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri (Body)"/>
-    </font>
-    <font>
-      <sz val="5"/>
-      <color theme="1"/>
-      <name val="Calibri (Body)"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -234,7 +307,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -260,10 +333,12 @@
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -271,74 +346,74 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -355,10 +430,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -396,234 +471,128 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -635,18 +604,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5" customWidth="1"/>
+    <col min="2" max="4" width="6.5" customWidth="1"/>
+    <col min="5" max="6" width="5.6640625" customWidth="1"/>
+    <col min="7" max="7" width="4.5" customWidth="1"/>
+    <col min="8" max="8" width="10.5" customWidth="1"/>
+    <col min="9" max="9" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -663,16 +632,22 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J1" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -689,13 +664,19 @@
         <v>63.9</v>
       </c>
       <c r="F2">
+        <v>0.1</v>
+      </c>
+      <c r="G2">
         <v>8</v>
       </c>
-      <c r="H2">
-        <v>103.2666451474047</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2">
+        <v>103.266645147405</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>0.5</v>
       </c>
@@ -712,13 +693,19 @@
         <v>63.9</v>
       </c>
       <c r="F3">
+        <v>0.1</v>
+      </c>
+      <c r="G3">
         <v>8</v>
       </c>
-      <c r="H3">
-        <v>109.5171219490359</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3">
+        <v>109.517121949036</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -735,13 +722,19 @@
         <v>63.9</v>
       </c>
       <c r="F4">
+        <v>0.1</v>
+      </c>
+      <c r="G4">
         <v>8</v>
       </c>
-      <c r="H4">
-        <v>118.5622199522259</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4">
+        <v>118.562219952226</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1.5</v>
       </c>
@@ -758,13 +751,19 @@
         <v>63.9</v>
       </c>
       <c r="F5">
+        <v>0.1</v>
+      </c>
+      <c r="G5">
         <v>8</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>128.26145173044</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2</v>
       </c>
@@ -781,13 +780,19 @@
         <v>63.9</v>
       </c>
       <c r="F6">
+        <v>0.1</v>
+      </c>
+      <c r="G6">
         <v>8</v>
       </c>
-      <c r="H6">
-        <v>139.47759676736621</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I6">
+        <v>139.47759676736601</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2.5</v>
       </c>
@@ -804,13 +809,19 @@
         <v>63.9</v>
       </c>
       <c r="F7">
+        <v>0.1</v>
+      </c>
+      <c r="G7">
         <v>8</v>
       </c>
-      <c r="H7">
-        <v>157.45475540611659</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I7">
+        <v>157.45475540611699</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>3</v>
       </c>
@@ -827,13 +838,19 @@
         <v>63.9</v>
       </c>
       <c r="F8">
+        <v>0.1</v>
+      </c>
+      <c r="G8">
         <v>8</v>
       </c>
-      <c r="H8">
-        <v>176.67484257811009</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I8">
+        <v>176.67484257811</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>3.5</v>
       </c>
@@ -850,13 +867,19 @@
         <v>63.9</v>
       </c>
       <c r="F9">
+        <v>0.1</v>
+      </c>
+      <c r="G9">
         <v>8</v>
       </c>
-      <c r="H9">
-        <v>206.30559856678639</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I9">
+        <v>206.30559856678599</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>4</v>
       </c>
@@ -873,13 +896,19 @@
         <v>63.9</v>
       </c>
       <c r="F10">
+        <v>0.1</v>
+      </c>
+      <c r="G10">
         <v>8</v>
       </c>
-      <c r="H10">
-        <v>241.73125573661341</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I10">
+        <v>241.73125573661301</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>4.5</v>
       </c>
@@ -896,13 +925,19 @@
         <v>63.9</v>
       </c>
       <c r="F11">
+        <v>0.1</v>
+      </c>
+      <c r="G11">
         <v>8</v>
       </c>
-      <c r="H11">
-        <v>292.54230463302218</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I11">
+        <v>292.54230463302201</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>5</v>
       </c>
@@ -919,13 +954,19 @@
         <v>63.9</v>
       </c>
       <c r="F12">
+        <v>0.1</v>
+      </c>
+      <c r="G12">
         <v>8</v>
       </c>
-      <c r="H12">
-        <v>358.5163873520986</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I12">
+        <v>358.516387352099</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>5.5</v>
       </c>
@@ -942,13 +983,19 @@
         <v>63.9</v>
       </c>
       <c r="F13">
+        <v>0.1</v>
+      </c>
+      <c r="G13">
         <v>8</v>
       </c>
-      <c r="H13">
-        <v>451.87830220093548</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I13">
+        <v>451.87830220093599</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>6</v>
       </c>
@@ -965,13 +1012,19 @@
         <v>63.9</v>
       </c>
       <c r="F14">
+        <v>0.1</v>
+      </c>
+      <c r="G14">
         <v>8</v>
       </c>
-      <c r="H14">
-        <v>556.1492605407293</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I14">
+        <v>556.14926054072896</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>6.5</v>
       </c>
@@ -988,13 +1041,19 @@
         <v>63.9</v>
       </c>
       <c r="F15">
+        <v>0.1</v>
+      </c>
+      <c r="G15">
         <v>8</v>
       </c>
-      <c r="H15">
-        <v>664.83832621171894</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I15">
+        <v>664.83832621171905</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>7</v>
       </c>
@@ -1011,13 +1070,19 @@
         <v>63.9</v>
       </c>
       <c r="F16">
+        <v>0.1</v>
+      </c>
+      <c r="G16">
         <v>8</v>
       </c>
-      <c r="H16">
-        <v>774.11239494016627</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I16">
+        <v>774.11239494016604</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>7.5</v>
       </c>
@@ -1034,13 +1099,19 @@
         <v>63.9</v>
       </c>
       <c r="F17">
+        <v>0.1</v>
+      </c>
+      <c r="G17">
         <v>8</v>
       </c>
-      <c r="H17">
-        <v>866.30883638573141</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I17">
+        <v>866.30883638573096</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>8</v>
       </c>
@@ -1057,13 +1128,19 @@
         <v>63.9</v>
       </c>
       <c r="F18">
+        <v>0.1</v>
+      </c>
+      <c r="G18">
         <v>8</v>
       </c>
-      <c r="H18">
-        <v>958.64539846598132</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I18">
+        <v>958.64539846598097</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>8.5</v>
       </c>
@@ -1080,13 +1157,19 @@
         <v>63.9</v>
       </c>
       <c r="F19">
+        <v>0.1</v>
+      </c>
+      <c r="G19">
         <v>8</v>
       </c>
-      <c r="H19">
-        <v>1023.121204941037</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I19">
+        <v>1023.12120494104</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>9</v>
       </c>
@@ -1103,13 +1186,19 @@
         <v>63.9</v>
       </c>
       <c r="F20">
+        <v>0.1</v>
+      </c>
+      <c r="G20">
         <v>8</v>
       </c>
-      <c r="H20">
-        <v>1070.296220679116</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I20">
+        <v>1070.2962206791201</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>9.5</v>
       </c>
@@ -1126,13 +1215,19 @@
         <v>63.9</v>
       </c>
       <c r="F21">
+        <v>0.1</v>
+      </c>
+      <c r="G21">
         <v>8</v>
       </c>
-      <c r="H21">
-        <v>1103.3322255784969</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I21">
+        <v>1103.3322255784999</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>10</v>
       </c>
@@ -1149,13 +1244,19 @@
         <v>63.9</v>
       </c>
       <c r="F22">
+        <v>0.1</v>
+      </c>
+      <c r="G22">
         <v>8</v>
       </c>
-      <c r="H22">
-        <v>1122.8401489081159</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I22">
+        <v>1122.84014890812</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>10.5</v>
       </c>
@@ -1172,13 +1273,19 @@
         <v>63.9</v>
       </c>
       <c r="F23">
+        <v>0.1</v>
+      </c>
+      <c r="G23">
         <v>8</v>
       </c>
-      <c r="H23">
-        <v>1132.2336331340809</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I23">
+        <v>1132.23363313408</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>11</v>
       </c>
@@ -1195,13 +1302,19 @@
         <v>63.9</v>
       </c>
       <c r="F24">
+        <v>0.1</v>
+      </c>
+      <c r="G24">
         <v>8</v>
       </c>
-      <c r="H24">
-        <v>1126.9964507486261</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I24">
+        <v>1126.99645074863</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>11.5</v>
       </c>
@@ -1218,13 +1331,19 @@
         <v>63.9</v>
       </c>
       <c r="F25">
+        <v>0.1</v>
+      </c>
+      <c r="G25">
         <v>8</v>
       </c>
-      <c r="H25">
-        <v>1111.2308491038209</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I25">
+        <v>1111.23084910382</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>12</v>
       </c>
@@ -1241,13 +1360,19 @@
         <v>63.9</v>
       </c>
       <c r="F26">
+        <v>0.1</v>
+      </c>
+      <c r="G26">
         <v>8</v>
       </c>
-      <c r="H26">
-        <v>1086.8587764746619</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I26">
+        <v>1086.8587764746601</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>12.5</v>
       </c>
@@ -1264,13 +1389,19 @@
         <v>63.9</v>
       </c>
       <c r="F27">
+        <v>0.1</v>
+      </c>
+      <c r="G27">
         <v>8</v>
       </c>
-      <c r="H27">
-        <v>1059.313928918147</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I27">
+        <v>1059.3139289181499</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>13</v>
       </c>
@@ -1287,13 +1418,19 @@
         <v>63.9</v>
       </c>
       <c r="F28">
+        <v>0.1</v>
+      </c>
+      <c r="G28">
         <v>8</v>
       </c>
-      <c r="H28">
-        <v>1036.463699316093</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I28">
+        <v>1036.46369931609</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>13.5</v>
       </c>
@@ -1310,13 +1447,19 @@
         <v>63.9</v>
       </c>
       <c r="F29">
+        <v>0.1</v>
+      </c>
+      <c r="G29">
         <v>8</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>1020.9378041781</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>14</v>
       </c>
@@ -1333,13 +1476,19 @@
         <v>63.9</v>
       </c>
       <c r="F30">
+        <v>0.1</v>
+      </c>
+      <c r="G30">
         <v>8</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>1023.04349858645</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>14.5</v>
       </c>
@@ -1356,13 +1505,19 @@
         <v>63.9</v>
       </c>
       <c r="F31">
+        <v>0.1</v>
+      </c>
+      <c r="G31">
         <v>8</v>
       </c>
-      <c r="H31">
-        <v>1037.307090499241</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I31">
+        <v>1037.3070904992401</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>15</v>
       </c>
@@ -1379,13 +1534,19 @@
         <v>63.9</v>
       </c>
       <c r="F32">
+        <v>0.1</v>
+      </c>
+      <c r="G32">
         <v>8</v>
       </c>
-      <c r="H32">
-        <v>1057.026489734292</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I32">
+        <v>1057.02648973429</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>15.5</v>
       </c>
@@ -1402,13 +1563,19 @@
         <v>63.9</v>
       </c>
       <c r="F33">
+        <v>0.1</v>
+      </c>
+      <c r="G33">
         <v>8</v>
       </c>
-      <c r="H33">
-        <v>1071.292210370261</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I33">
+        <v>1071.2922103702599</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>16</v>
       </c>
@@ -1425,13 +1592,19 @@
         <v>63.9</v>
       </c>
       <c r="F34">
+        <v>0.1</v>
+      </c>
+      <c r="G34">
         <v>8</v>
       </c>
-      <c r="H34">
-        <v>1083.196658045066</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I34">
+        <v>1083.1966580450701</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>16.5</v>
       </c>
@@ -1448,13 +1621,19 @@
         <v>63.9</v>
       </c>
       <c r="F35">
+        <v>0.1</v>
+      </c>
+      <c r="G35">
         <v>8</v>
       </c>
-      <c r="H35">
-        <v>1083.821479765003</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I35">
+        <v>1083.821479765</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>17</v>
       </c>
@@ -1471,13 +1650,19 @@
         <v>63.9</v>
       </c>
       <c r="F36">
+        <v>0.1</v>
+      </c>
+      <c r="G36">
         <v>8</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>1076.05064936554</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>17.5</v>
       </c>
@@ -1494,13 +1679,19 @@
         <v>63.9</v>
       </c>
       <c r="F37">
+        <v>0.1</v>
+      </c>
+      <c r="G37">
         <v>8</v>
       </c>
-      <c r="H37">
-        <v>1050.6902493123271</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I37">
+        <v>1050.69024931233</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>18</v>
       </c>
@@ -1517,13 +1708,19 @@
         <v>63.9</v>
       </c>
       <c r="F38">
+        <v>0.1</v>
+      </c>
+      <c r="G38">
         <v>8</v>
       </c>
-      <c r="H38">
-        <v>1020.793318943654</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I38">
+        <v>1020.79331894365</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>18.5</v>
       </c>
@@ -1540,13 +1737,19 @@
         <v>63.9</v>
       </c>
       <c r="F39">
+        <v>0.1</v>
+      </c>
+      <c r="G39">
         <v>8</v>
       </c>
-      <c r="H39">
-        <v>964.9321219650634</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I39">
+        <v>964.93212196506295</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>19</v>
       </c>
@@ -1563,13 +1766,19 @@
         <v>63.9</v>
       </c>
       <c r="F40">
+        <v>0.1</v>
+      </c>
+      <c r="G40">
         <v>8</v>
       </c>
-      <c r="H40">
-        <v>900.71416109662675</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I40">
+        <v>900.71416109662698</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>19.5</v>
       </c>
@@ -1586,13 +1795,19 @@
         <v>63.9</v>
       </c>
       <c r="F41">
+        <v>0.1</v>
+      </c>
+      <c r="G41">
         <v>8</v>
       </c>
-      <c r="H41">
-        <v>808.45840956724544</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I41">
+        <v>808.45840956724498</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>20</v>
       </c>
@@ -1609,13 +1824,19 @@
         <v>63.9</v>
       </c>
       <c r="F42">
+        <v>0.1</v>
+      </c>
+      <c r="G42">
         <v>8</v>
       </c>
-      <c r="H42">
-        <v>701.17758093082239</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I42">
+        <v>701.17758093082205</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>20.5</v>
       </c>
@@ -1632,13 +1853,19 @@
         <v>63.9</v>
       </c>
       <c r="F43">
+        <v>0.1</v>
+      </c>
+      <c r="G43">
         <v>8</v>
       </c>
-      <c r="H43">
-        <v>588.95585573114056</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I43">
+        <v>588.95585573114101</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>21</v>
       </c>
@@ -1655,13 +1882,19 @@
         <v>63.9</v>
       </c>
       <c r="F44">
+        <v>0.1</v>
+      </c>
+      <c r="G44">
         <v>8</v>
       </c>
-      <c r="H44">
-        <v>494.23172702690789</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I44">
+        <v>494.231727026908</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>21.5</v>
       </c>
@@ -1678,13 +1911,19 @@
         <v>63.9</v>
       </c>
       <c r="F45">
+        <v>0.1</v>
+      </c>
+      <c r="G45">
         <v>8</v>
       </c>
-      <c r="H45">
-        <v>392.48312065616273</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I45">
+        <v>392.48312065616301</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>22</v>
       </c>
@@ -1701,13 +1940,19 @@
         <v>63.9</v>
       </c>
       <c r="F46">
+        <v>0.1</v>
+      </c>
+      <c r="G46">
         <v>8</v>
       </c>
-      <c r="H46">
-        <v>326.81646225366308</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I46">
+        <v>326.81646225366302</v>
+      </c>
+      <c r="J46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>22.5</v>
       </c>
@@ -1724,13 +1969,19 @@
         <v>63.9</v>
       </c>
       <c r="F47">
+        <v>0.1</v>
+      </c>
+      <c r="G47">
         <v>8</v>
       </c>
-      <c r="H47">
-        <v>264.70549673174531</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I47">
+        <v>264.70549673174497</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>23</v>
       </c>
@@ -1747,13 +1998,19 @@
         <v>63.9</v>
       </c>
       <c r="F48">
+        <v>0.1</v>
+      </c>
+      <c r="G48">
         <v>8</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>212.57939693206399</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>23.5</v>
       </c>
@@ -1770,13 +2027,19 @@
         <v>63.9</v>
       </c>
       <c r="F49">
+        <v>0.1</v>
+      </c>
+      <c r="G49">
         <v>8</v>
       </c>
-      <c r="H49">
-        <v>184.64560650066929</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I49">
+        <v>184.645606500669</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>24</v>
       </c>
@@ -1793,13 +2056,19 @@
         <v>63.9</v>
       </c>
       <c r="F50">
+        <v>0.1</v>
+      </c>
+      <c r="G50">
         <v>8</v>
       </c>
-      <c r="H50">
-        <v>161.4496825639493</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I50">
+        <v>161.44968256394901</v>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>24.5</v>
       </c>
@@ -1816,13 +2085,19 @@
         <v>63.9</v>
       </c>
       <c r="F51">
+        <v>0.1</v>
+      </c>
+      <c r="G51">
         <v>8</v>
       </c>
-      <c r="H51">
-        <v>147.14958375748131</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I51">
+        <v>147.149583757481</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>25</v>
       </c>
@@ -1839,13 +2114,19 @@
         <v>63.9</v>
       </c>
       <c r="F52">
+        <v>0.1</v>
+      </c>
+      <c r="G52">
         <v>8</v>
       </c>
-      <c r="H52">
-        <v>132.29512462672241</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I52">
+        <v>132.29512462672199</v>
+      </c>
+      <c r="J52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>25.5</v>
       </c>
@@ -1862,13 +2143,19 @@
         <v>63.9</v>
       </c>
       <c r="F53">
+        <v>0.1</v>
+      </c>
+      <c r="G53">
         <v>8</v>
       </c>
-      <c r="H53">
+      <c r="I53">
         <v>122.343777937417</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>26</v>
       </c>
@@ -1885,13 +2172,19 @@
         <v>63.9</v>
       </c>
       <c r="F54">
+        <v>0.1</v>
+      </c>
+      <c r="G54">
         <v>8</v>
       </c>
-      <c r="H54">
-        <v>114.65164630305139</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I54">
+        <v>114.651646303051</v>
+      </c>
+      <c r="J54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>26.5</v>
       </c>
@@ -1908,56 +2201,63 @@
         <v>63.9</v>
       </c>
       <c r="F55">
+        <v>0.1</v>
+      </c>
+      <c r="G55">
         <v>8</v>
       </c>
-      <c r="H55">
-        <v>109.9909087152206</v>
+      <c r="I55">
+        <v>109.990908715221</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E72F9668-A97B-CE41-BACA-47C7E4EC7F9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.1640625" customWidth="1"/>
+    <col min="2" max="2" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="4" max="4" width="8.5" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="6" max="6" width="8.5" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2">
@@ -1980,7 +2280,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3">
@@ -2003,7 +2303,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4">
@@ -2026,7 +2326,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5">
@@ -2049,30 +2349,30 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>1200</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>49.5</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>1.262</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>1.272</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>1.2470000000000001</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>2.52</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
+      <c r="A7" s="4">
         <v>1</v>
       </c>
       <c r="B7">
@@ -2095,7 +2395,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
+      <c r="A8" s="4">
         <v>2</v>
       </c>
       <c r="B8">
@@ -2118,7 +2418,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
+      <c r="A9" s="4">
         <v>3</v>
       </c>
       <c r="B9">
@@ -2141,7 +2441,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
+      <c r="A10" s="4">
         <v>4</v>
       </c>
       <c r="B10">
@@ -2164,30 +2464,30 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>5</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="3">
         <v>1200</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>41.9</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
         <v>1.25</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="3">
         <v>1.26</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="3">
         <v>1.2430000000000001</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="3">
         <v>2.5139999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
+      <c r="A12" s="4">
         <v>1</v>
       </c>
       <c r="B12">
@@ -2210,7 +2510,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="2">
+      <c r="A13" s="4">
         <v>2</v>
       </c>
       <c r="B13">
@@ -2233,7 +2533,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="2">
+      <c r="A14" s="4">
         <v>3</v>
       </c>
       <c r="B14">
@@ -2256,7 +2556,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="2">
+      <c r="A15" s="4">
         <v>4</v>
       </c>
       <c r="B15">
@@ -2279,30 +2579,30 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
+      <c r="A16" s="2">
         <v>5</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="3">
         <v>1200</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="3">
         <v>34.799999999999997</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="3">
         <v>1.2789999999999999</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="3">
         <v>1.29</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="3">
         <v>1.2709999999999999</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="3">
         <v>2.5139999999999998</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="2">
+      <c r="A17" s="4">
         <v>1</v>
       </c>
       <c r="B17">
@@ -2325,7 +2625,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="2">
+      <c r="A18" s="4">
         <v>2</v>
       </c>
       <c r="B18">
@@ -2348,7 +2648,7 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="2">
+      <c r="A19" s="4">
         <v>3</v>
       </c>
       <c r="B19">
@@ -2371,7 +2671,7 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="2">
+      <c r="A20" s="4">
         <v>4</v>
       </c>
       <c r="B20">
@@ -2394,30 +2694,30 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="3">
+      <c r="A21" s="2">
         <v>5</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="3">
         <v>1200</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="3">
         <v>26.1</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="3">
         <v>1.2729999999999999</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="3">
         <v>1.28</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="3">
         <v>1.2669999999999999</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="3">
         <v>2.5139999999999998</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="2">
+      <c r="A22" s="4">
         <v>1</v>
       </c>
       <c r="B22">
@@ -2440,7 +2740,7 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="2">
+      <c r="A23" s="4">
         <v>2</v>
       </c>
       <c r="B23">
@@ -2463,7 +2763,7 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="2">
+      <c r="A24" s="4">
         <v>3</v>
       </c>
       <c r="B24">
@@ -2486,7 +2786,7 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="2">
+      <c r="A25" s="4">
         <v>4</v>
       </c>
       <c r="B25">
@@ -2509,7 +2809,7 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="2">
+      <c r="A26" s="4">
         <v>5</v>
       </c>
       <c r="B26">
@@ -2532,97 +2832,98 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q87"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="29" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.1640625" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="31" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="10" width="29" customWidth="1"/>
+    <col min="11" max="11" width="19" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="17.6640625" customWidth="1"/>
+    <col min="14" max="14" width="20.1640625" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="16" max="16" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="3" t="s">
+    <row r="1" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="J1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="L1" s="9" t="s">
+      <c r="K1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="6"/>
+      <c r="B2" t="s">
         <v>27</v>
       </c>
-      <c r="M1" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="11"/>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="8">
-        <v>1</v>
-      </c>
-      <c r="D2" s="6">
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2">
         <f>Metingen!E2-Metingen!F2</f>
         <v>1.6999999999999904E-2</v>
       </c>
-      <c r="E2" s="6">
-        <f>D2/2</f>
+      <c r="E2">
+        <f t="shared" ref="E2:E26" si="0">D2/2</f>
         <v>8.499999999999952E-3</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2">
         <f>Metingen!D2</f>
         <v>1.2549999999999999</v>
       </c>
-      <c r="G2" s="6">
-        <f>E2/(2*F2)</f>
+      <c r="G2">
+        <f t="shared" ref="G2:G26" si="1">E2/(2*F2)</f>
         <v>3.3864541832669135E-3</v>
       </c>
-      <c r="H2" s="6">
-        <f>G2/PI()*180</f>
+      <c r="H2">
+        <f t="shared" ref="H2:H26" si="2">G2/PI()*180</f>
         <v>0.19402953221561636</v>
       </c>
       <c r="I2">
@@ -2630,47 +2931,47 @@
         <v>1.0031298904538339</v>
       </c>
       <c r="J2">
-        <f>$A$16*I2</f>
+        <f t="shared" ref="J2:J26" si="3">$A$16*I2</f>
         <v>0.81142441849107527</v>
       </c>
       <c r="K2">
-        <f>J2*10^(-3)</f>
+        <f t="shared" ref="K2:K26" si="4">J2*10^(-3)</f>
         <v>8.1142441849107528E-4</v>
       </c>
-      <c r="L2" s="6">
-        <f>G2/(K2*$A$10)</f>
+      <c r="L2">
+        <f t="shared" ref="L2:L26" si="5">G2/(K2*$A$10)</f>
         <v>20.867342084456634</v>
       </c>
-      <c r="M2" s="6">
-        <f>L2/PI()*180</f>
+      <c r="M2">
+        <f t="shared" ref="M2:M26" si="6">L2/PI()*180</f>
         <v>1195.6106310950909</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="8">
+      <c r="A3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="4">
         <v>2</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3">
         <f>Metingen!E3-Metingen!F3</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="E3" s="6">
-        <f t="shared" ref="E3:E26" si="0">D3/2</f>
+      <c r="E3">
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3">
         <f>Metingen!D3</f>
         <v>1.256</v>
       </c>
-      <c r="G3" s="6">
-        <f>E3/(2*F3)</f>
+      <c r="G3">
+        <f t="shared" si="1"/>
         <v>3.9808917197452264E-3</v>
       </c>
-      <c r="H3" s="6">
-        <f t="shared" ref="H3:H26" si="1">G3/PI()*180</f>
+      <c r="H3">
+        <f t="shared" si="2"/>
         <v>0.22808829423997759</v>
       </c>
       <c r="I3">
@@ -2678,47 +2979,47 @@
         <v>1.0125195618153364</v>
       </c>
       <c r="J3">
-        <f>$A$16*I3</f>
+        <f t="shared" si="3"/>
         <v>0.81901965485760642</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K26" si="2">J3*10^(-3)</f>
+        <f t="shared" si="4"/>
         <v>8.1901965485760644E-4</v>
       </c>
-      <c r="L3" s="6">
-        <f>G3/(K3*$A$10)</f>
+      <c r="L3">
+        <f t="shared" si="5"/>
         <v>24.302785019471468</v>
       </c>
-      <c r="M3" s="6">
-        <f t="shared" ref="M3:M26" si="3">L3/PI()*180</f>
+      <c r="M3">
+        <f t="shared" si="6"/>
         <v>1392.4470120294775</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
+      <c r="A4" s="4">
         <v>63.9</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="4">
         <v>3</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4">
         <f>Metingen!E4-Metingen!F4</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4">
         <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4">
         <f>Metingen!D4</f>
         <v>1.25</v>
       </c>
-      <c r="G4" s="6">
-        <f>E4/(2*F4)</f>
+      <c r="G4">
+        <f t="shared" si="1"/>
         <v>4.0000000000000036E-3</v>
       </c>
-      <c r="H4" s="6">
-        <f t="shared" si="1"/>
+      <c r="H4">
+        <f t="shared" si="2"/>
         <v>0.22918311805232949</v>
       </c>
       <c r="I4">
@@ -2726,45 +3027,45 @@
         <v>1.0031298904538339</v>
       </c>
       <c r="J4">
-        <f>$A$16*I4</f>
+        <f t="shared" si="3"/>
         <v>0.81142441849107527</v>
       </c>
       <c r="K4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8.1142441849107528E-4</v>
       </c>
-      <c r="L4" s="6">
-        <f>G4/(K4*$A$10)</f>
+      <c r="L4">
+        <f t="shared" si="5"/>
         <v>24.648013473875995</v>
       </c>
-      <c r="M4" s="6">
-        <f t="shared" si="3"/>
+      <c r="M4">
+        <f t="shared" si="6"/>
         <v>1412.2271454346812</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
-      <c r="C5" s="8">
+      <c r="A5" s="4"/>
+      <c r="C5" s="4">
         <v>4</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5">
         <f>Metingen!E5-Metingen!F5</f>
         <v>2.4999999999999911E-2</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5">
         <f t="shared" si="0"/>
         <v>1.2499999999999956E-2</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5">
         <f>Metingen!D5</f>
         <v>1.2669999999999999</v>
       </c>
-      <c r="G5" s="6">
-        <f>E5/(2*F5)</f>
+      <c r="G5">
+        <f t="shared" si="1"/>
         <v>4.9329123914759101E-3</v>
       </c>
-      <c r="H5" s="6">
-        <f t="shared" si="1"/>
+      <c r="H5">
+        <f t="shared" si="2"/>
         <v>0.28263506073935535</v>
       </c>
       <c r="I5">
@@ -2772,99 +3073,99 @@
         <v>1.0015649452269171</v>
       </c>
       <c r="J5">
-        <f>$A$16*I5</f>
+        <f t="shared" si="3"/>
         <v>0.81015854576332025</v>
       </c>
       <c r="K5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8.1015854576332023E-4</v>
       </c>
-      <c r="L5" s="6">
-        <f>G5/(K5*$A$10)</f>
+      <c r="L5">
+        <f t="shared" si="5"/>
         <v>30.444117495719233</v>
       </c>
-      <c r="M5" s="6">
-        <f t="shared" si="3"/>
+      <c r="M5">
+        <f t="shared" si="6"/>
         <v>1744.3194435051012</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="16">
+      <c r="A6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="2">
         <v>5</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="3">
         <f>Metingen!E6-Metingen!F6</f>
         <v>2.4999999999999911E-2</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="3">
         <f t="shared" si="0"/>
         <v>1.2499999999999956E-2</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="3">
         <f>Metingen!D6</f>
         <v>1.262</v>
       </c>
-      <c r="G6" s="15">
-        <f>E6/(2*F6)</f>
+      <c r="G6" s="3">
+        <f t="shared" si="1"/>
         <v>4.9524564183835006E-3</v>
       </c>
-      <c r="H6" s="15">
-        <f t="shared" si="1"/>
+      <c r="H6" s="3">
+        <f t="shared" si="2"/>
         <v>0.28375485099585046</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="3">
         <f>Metingen!C6/$A$4</f>
         <v>0.77464788732394363</v>
       </c>
-      <c r="J6" s="4">
-        <f>$A$16*I6</f>
+      <c r="J6" s="3">
+        <f t="shared" si="3"/>
         <v>0.62660700023881788</v>
       </c>
-      <c r="K6" s="4">
-        <f t="shared" si="2"/>
+      <c r="K6" s="3">
+        <f t="shared" si="4"/>
         <v>6.2660700023881792E-4</v>
       </c>
-      <c r="L6" s="15">
-        <f>G6/(K6*$A$10)</f>
+      <c r="L6" s="3">
+        <f t="shared" si="5"/>
         <v>39.518042540986428</v>
       </c>
-      <c r="M6" s="15">
-        <f t="shared" si="3"/>
+      <c r="M6" s="3">
+        <f t="shared" si="6"/>
         <v>2264.2170522169658</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="13">
+      <c r="A7" s="6">
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="8">
-        <v>1</v>
-      </c>
-      <c r="D7" s="6">
+        <v>30</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1</v>
+      </c>
+      <c r="D7">
         <f>Metingen!E7-Metingen!F7</f>
         <v>1.8000000000000016E-2</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7">
         <f t="shared" si="0"/>
         <v>9.000000000000008E-3</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7">
         <f>Metingen!D7</f>
         <v>1.246</v>
       </c>
-      <c r="G7" s="6">
-        <f>E7/(2*F7)</f>
+      <c r="G7">
+        <f t="shared" si="1"/>
         <v>3.6115569823435023E-3</v>
       </c>
-      <c r="H7" s="6">
-        <f t="shared" si="1"/>
+      <c r="H7">
+        <f t="shared" si="2"/>
         <v>0.20692697255928624</v>
       </c>
       <c r="I7">
@@ -2872,45 +3173,45 @@
         <v>0.90140845070422537</v>
       </c>
       <c r="J7">
-        <f>$A$16*I7</f>
+        <f t="shared" si="3"/>
         <v>0.72914269118698816</v>
       </c>
       <c r="K7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>7.2914269118698818E-4</v>
       </c>
-      <c r="L7" s="6">
-        <f>G7/(K7*$A$10)</f>
+      <c r="L7">
+        <f t="shared" si="5"/>
         <v>24.765776479663849</v>
       </c>
-      <c r="M7" s="6">
-        <f t="shared" si="3"/>
+      <c r="M7">
+        <f t="shared" si="6"/>
         <v>1418.9744686491001</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="11"/>
-      <c r="C8" s="8">
+      <c r="A8" s="6"/>
+      <c r="C8" s="4">
         <v>2</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8">
         <f>Metingen!E8-Metingen!F8</f>
         <v>1.8000000000000016E-2</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8">
         <f t="shared" si="0"/>
         <v>9.000000000000008E-3</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8">
         <f>Metingen!D8</f>
         <v>1.2529999999999999</v>
       </c>
-      <c r="G8" s="6">
-        <f>E8/(2*F8)</f>
+      <c r="G8">
+        <f t="shared" si="1"/>
         <v>3.5913806863527571E-3</v>
       </c>
-      <c r="H8" s="6">
-        <f t="shared" si="1"/>
+      <c r="H8">
+        <f t="shared" si="2"/>
         <v>0.20577095595280984</v>
       </c>
       <c r="I8">
@@ -2918,47 +3219,47 @@
         <v>0.89827856025039121</v>
       </c>
       <c r="J8">
-        <f>$A$16*I8</f>
+        <f t="shared" si="3"/>
         <v>0.72661094573147778</v>
       </c>
       <c r="K8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>7.2661094573147776E-4</v>
       </c>
-      <c r="L8" s="6">
-        <f>G8/(K8*$A$10)</f>
+      <c r="L8">
+        <f t="shared" si="5"/>
         <v>24.713230012915105</v>
       </c>
-      <c r="M8" s="6">
-        <f t="shared" si="3"/>
+      <c r="M8">
+        <f t="shared" si="6"/>
         <v>1415.9637778760725</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="8">
+      <c r="A9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="4">
         <v>3</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9">
         <f>Metingen!E9-Metingen!F9</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9">
         <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9">
         <f>Metingen!D9</f>
         <v>1.2450000000000001</v>
       </c>
-      <c r="G9" s="6">
-        <f>E9/(2*F9)</f>
+      <c r="G9">
+        <f t="shared" si="1"/>
         <v>4.0160642570281156E-3</v>
       </c>
-      <c r="H9" s="6">
-        <f t="shared" si="1"/>
+      <c r="H9">
+        <f t="shared" si="2"/>
         <v>0.23010353218105367</v>
       </c>
       <c r="I9">
@@ -2966,47 +3267,47 @@
         <v>0.9061032863849765</v>
       </c>
       <c r="J9">
-        <f>$A$16*I9</f>
+        <f t="shared" si="3"/>
         <v>0.73294030937025367</v>
       </c>
       <c r="K9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>7.3294030937025366E-4</v>
       </c>
-      <c r="L9" s="6">
-        <f>G9/(K9*$A$10)</f>
+      <c r="L9">
+        <f t="shared" si="5"/>
         <v>27.396939462087573</v>
       </c>
-      <c r="M9" s="6">
-        <f t="shared" si="3"/>
+      <c r="M9">
+        <f t="shared" si="6"/>
         <v>1569.7290027530339</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="13">
+      <c r="A10" s="6">
         <v>0.2</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="4">
         <v>4</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10">
         <f>Metingen!E10-Metingen!F10</f>
         <v>1.9999999999999796E-2</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10">
         <f t="shared" si="0"/>
         <v>9.9999999999998979E-3</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10">
         <f>Metingen!D10</f>
         <v>1.2430000000000001</v>
       </c>
-      <c r="G10" s="6">
-        <f>E10/(2*F10)</f>
+      <c r="G10">
+        <f t="shared" si="1"/>
         <v>4.0225261464199103E-3</v>
       </c>
-      <c r="H10" s="6">
-        <f t="shared" si="1"/>
+      <c r="H10">
+        <f t="shared" si="2"/>
         <v>0.23047377117088388</v>
       </c>
       <c r="I10">
@@ -3014,97 +3315,97 @@
         <v>0.90453834115805942</v>
       </c>
       <c r="J10">
-        <f>$A$16*I10</f>
+        <f t="shared" si="3"/>
         <v>0.73167443664249854</v>
       </c>
       <c r="K10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>7.316744366424985E-4</v>
       </c>
-      <c r="L10" s="6">
-        <f>G10/(K10*$A$10)</f>
+      <c r="L10">
+        <f t="shared" si="5"/>
         <v>27.48849723982735</v>
       </c>
-      <c r="M10" s="6">
-        <f t="shared" si="3"/>
+      <c r="M10">
+        <f t="shared" si="6"/>
         <v>1574.9748769991197</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="16">
+      <c r="A11" s="4"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="2">
         <v>5</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="3">
         <f>Metingen!E11-Metingen!F11</f>
         <v>1.6999999999999904E-2</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="3">
         <f t="shared" si="0"/>
         <v>8.499999999999952E-3</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="3">
         <f>Metingen!D11</f>
         <v>1.25</v>
       </c>
-      <c r="G11" s="15">
-        <f>E11/(2*F11)</f>
+      <c r="G11" s="3">
+        <f t="shared" si="1"/>
         <v>3.3999999999999807E-3</v>
       </c>
-      <c r="H11" s="15">
-        <f t="shared" si="1"/>
+      <c r="H11" s="3">
+        <f t="shared" si="2"/>
         <v>0.1948056503444788</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="3">
         <f>Metingen!C11/$A$4</f>
         <v>0.65571205007824729</v>
       </c>
-      <c r="J11" s="4">
-        <f>$A$16*I11</f>
+      <c r="J11" s="3">
+        <f t="shared" si="3"/>
         <v>0.53040067292942372</v>
       </c>
-      <c r="K11" s="4">
-        <f t="shared" si="2"/>
+      <c r="K11" s="3">
+        <f t="shared" si="4"/>
         <v>5.3040067292942376E-4</v>
       </c>
-      <c r="L11" s="15">
-        <f>G11/(K11*$A$10)</f>
+      <c r="L11" s="3">
+        <f t="shared" si="5"/>
         <v>32.051241387210609</v>
       </c>
-      <c r="M11" s="15">
-        <f t="shared" si="3"/>
+      <c r="M11" s="3">
+        <f t="shared" si="6"/>
         <v>1836.4008596421979</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
-        <v>25</v>
+      <c r="A12" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="8">
-        <v>1</v>
-      </c>
-      <c r="D12" s="6">
+        <v>33</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12">
         <f>Metingen!E12-Metingen!F12</f>
         <v>2.0999999999999908E-2</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12">
         <f t="shared" si="0"/>
         <v>1.0499999999999954E-2</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12">
         <f>Metingen!D12</f>
         <v>1.2589999999999999</v>
       </c>
-      <c r="G12" s="6">
-        <f>E12/(2*F12)</f>
+      <c r="G12">
+        <f t="shared" si="1"/>
         <v>4.1699761715647161E-3</v>
       </c>
-      <c r="H12" s="6">
-        <f t="shared" si="1"/>
+      <c r="H12">
+        <f t="shared" si="2"/>
         <v>0.23892203530077913</v>
       </c>
       <c r="I12">
@@ -3112,47 +3413,47 @@
         <v>1.2097026604068857</v>
       </c>
       <c r="J12">
-        <f>$A$16*I12</f>
+        <f t="shared" si="3"/>
         <v>0.97851961855476011</v>
       </c>
       <c r="K12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9.7851961855476011E-4</v>
       </c>
-      <c r="L12" s="6">
-        <f>G12/(K12*$A$10)</f>
+      <c r="L12">
+        <f t="shared" si="5"/>
         <v>21.307575711786075</v>
       </c>
-      <c r="M12" s="6">
-        <f t="shared" si="3"/>
+      <c r="M12">
+        <f t="shared" si="6"/>
         <v>1220.8341599408031</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="13">
-        <v>1</v>
-      </c>
-      <c r="C13" s="8">
+      <c r="A13" s="6">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4">
         <v>2</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13">
         <f>Metingen!E13-Metingen!F13</f>
         <v>2.200000000000002E-2</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13">
         <f t="shared" si="0"/>
         <v>1.100000000000001E-2</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13">
         <f>Metingen!D13</f>
         <v>1.27</v>
       </c>
-      <c r="G13" s="6">
-        <f>E13/(2*F13)</f>
+      <c r="G13">
+        <f t="shared" si="1"/>
         <v>4.3307086614173262E-3</v>
       </c>
-      <c r="H13" s="6">
-        <f t="shared" si="1"/>
+      <c r="H13">
+        <f t="shared" si="2"/>
         <v>0.24813132859996301</v>
       </c>
       <c r="I13">
@@ -3160,45 +3461,45 @@
         <v>1.2065727699530515</v>
       </c>
       <c r="J13">
-        <f>$A$16*I13</f>
+        <f t="shared" si="3"/>
         <v>0.97598787309924973</v>
       </c>
       <c r="K13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9.7598787309924979E-4</v>
       </c>
-      <c r="L13" s="6">
-        <f>G13/(K13*$A$10)</f>
+      <c r="L13">
+        <f t="shared" si="5"/>
         <v>22.18628315362751</v>
       </c>
-      <c r="M13" s="6">
-        <f t="shared" si="3"/>
+      <c r="M13">
+        <f t="shared" si="6"/>
         <v>1271.1803877850546</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="11"/>
-      <c r="C14" s="8">
+      <c r="A14" s="6"/>
+      <c r="C14" s="4">
         <v>3</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14">
         <f>Metingen!E14-Metingen!F14</f>
         <v>2.2999999999999909E-2</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14">
         <f t="shared" si="0"/>
         <v>1.1499999999999955E-2</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14">
         <f>Metingen!D14</f>
         <v>1.2709999999999999</v>
       </c>
-      <c r="G14" s="6">
-        <f>E14/(2*F14)</f>
+      <c r="G14">
+        <f t="shared" si="1"/>
         <v>4.5239968528717374E-3</v>
       </c>
-      <c r="H14" s="6">
-        <f t="shared" si="1"/>
+      <c r="H14">
+        <f t="shared" si="2"/>
         <v>0.25920592620001742</v>
       </c>
       <c r="I14">
@@ -3206,47 +3507,47 @@
         <v>1.2065727699530515</v>
       </c>
       <c r="J14">
-        <f>$A$16*I14</f>
+        <f t="shared" si="3"/>
         <v>0.97598787309924973</v>
       </c>
       <c r="K14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9.7598787309924979E-4</v>
       </c>
-      <c r="L14" s="6">
-        <f>G14/(K14*$A$10)</f>
+      <c r="L14">
+        <f t="shared" si="5"/>
         <v>23.17650135603521</v>
       </c>
-      <c r="M14" s="6">
-        <f t="shared" si="3"/>
+      <c r="M14">
+        <f t="shared" si="6"/>
         <v>1327.9157115800467</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="8">
+      <c r="A15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="4">
         <v>4</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15">
         <f>Metingen!E15-Metingen!F15</f>
         <v>2.8999999999999915E-2</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15">
         <f t="shared" si="0"/>
         <v>1.4499999999999957E-2</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15">
         <f>Metingen!D15</f>
         <v>1.252</v>
       </c>
-      <c r="G15" s="6">
-        <f>E15/(2*F15)</f>
+      <c r="G15">
+        <f t="shared" si="1"/>
         <v>5.7907348242811334E-3</v>
       </c>
-      <c r="H15" s="6">
-        <f t="shared" si="1"/>
+      <c r="H15">
+        <f t="shared" si="2"/>
         <v>0.33178466571073933</v>
       </c>
       <c r="I15">
@@ -3254,98 +3555,98 @@
         <v>1.1987480438184663</v>
       </c>
       <c r="J15">
-        <f>$A$16*I15</f>
+        <f t="shared" si="3"/>
         <v>0.96965850946047383</v>
       </c>
       <c r="K15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9.6965850946047389E-4</v>
       </c>
-      <c r="L15" s="6">
-        <f>G15/(K15*$A$10)</f>
+      <c r="L15">
+        <f t="shared" si="5"/>
         <v>29.859660735113572</v>
       </c>
-      <c r="M15" s="6">
-        <f t="shared" si="3"/>
+      <c r="M15">
+        <f t="shared" si="6"/>
         <v>1710.8325378145087</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="13">
+      <c r="A16" s="6">
         <f>(A19/$A$7)*10^(3)</f>
         <v>0.808892673035565</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="16">
+      <c r="B16" s="7"/>
+      <c r="C16" s="2">
         <v>5</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="3">
         <f>Metingen!E16-Metingen!F16</f>
         <v>1.9000000000000128E-2</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="3">
         <f t="shared" si="0"/>
         <v>9.5000000000000639E-3</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="3">
         <f>Metingen!D16</f>
         <v>1.2789999999999999</v>
       </c>
-      <c r="G16" s="15">
-        <f>E16/(2*F16)</f>
+      <c r="G16" s="3">
+        <f t="shared" si="1"/>
         <v>3.7138389366692982E-3</v>
       </c>
-      <c r="H16" s="15">
-        <f t="shared" si="1"/>
+      <c r="H16" s="3">
+        <f t="shared" si="2"/>
         <v>0.21278729686250419</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="3">
         <f>Metingen!C16/$A$4</f>
         <v>0.54460093896713613</v>
       </c>
-      <c r="J16" s="4">
-        <f>$A$16*I16</f>
+      <c r="J16" s="3">
+        <f t="shared" si="3"/>
         <v>0.44052370925880535</v>
       </c>
-      <c r="K16" s="4">
-        <f t="shared" si="2"/>
+      <c r="K16" s="3">
+        <f t="shared" si="4"/>
         <v>4.4052370925880534E-4</v>
       </c>
-      <c r="L16" s="15">
-        <f>G16/(K16*$A$10)</f>
+      <c r="L16" s="3">
+        <f t="shared" si="5"/>
         <v>42.152543195892292</v>
       </c>
-      <c r="M16" s="15">
-        <f t="shared" si="3"/>
+      <c r="M16" s="3">
+        <f t="shared" si="6"/>
         <v>2415.1628208675234</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A17" s="11"/>
+      <c r="A17" s="6"/>
       <c r="B17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="8">
-        <v>1</v>
-      </c>
-      <c r="D17" s="6">
+        <v>35</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1</v>
+      </c>
+      <c r="D17">
         <f>Metingen!E17-Metingen!F17</f>
         <v>1.6000000000000014E-2</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17">
         <f t="shared" si="0"/>
         <v>8.0000000000000071E-3</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17">
         <f>Metingen!D17</f>
         <v>1.254</v>
       </c>
-      <c r="G17" s="6">
-        <f>E17/(2*F17)</f>
+      <c r="G17">
+        <f t="shared" si="1"/>
         <v>3.1897926634768766E-3</v>
       </c>
-      <c r="H17" s="6">
-        <f t="shared" si="1"/>
+      <c r="H17">
+        <f t="shared" si="2"/>
         <v>0.18276165713901871</v>
       </c>
       <c r="I17">
@@ -3353,47 +3654,47 @@
         <v>0.78247261345852892</v>
       </c>
       <c r="J17">
-        <f>$A$16*I17</f>
+        <f t="shared" si="3"/>
         <v>0.63293636387759389</v>
       </c>
       <c r="K17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6.3293636387759392E-4</v>
       </c>
-      <c r="L17" s="6">
-        <f>G17/(K17*$A$10)</f>
+      <c r="L17">
+        <f t="shared" si="5"/>
         <v>25.198367841713733</v>
       </c>
-      <c r="M17" s="6">
-        <f t="shared" si="3"/>
+      <c r="M17">
+        <f t="shared" si="6"/>
         <v>1443.7601279483742</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="8">
+      <c r="A18" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="4">
         <v>2</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18">
         <f>Metingen!E18-Metingen!F18</f>
         <v>1.8000000000000016E-2</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18">
         <f t="shared" si="0"/>
         <v>9.000000000000008E-3</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18">
         <f>Metingen!D18</f>
         <v>1.2729999999999999</v>
       </c>
-      <c r="G18" s="6">
-        <f>E18/(2*F18)</f>
+      <c r="G18">
+        <f t="shared" si="1"/>
         <v>3.5349567949725094E-3</v>
       </c>
-      <c r="H18" s="6">
-        <f t="shared" si="1"/>
+      <c r="H18">
+        <f t="shared" si="2"/>
         <v>0.20253810511301706</v>
       </c>
       <c r="I18">
@@ -3401,47 +3702,47 @@
         <v>0.784037558685446</v>
       </c>
       <c r="J18">
-        <f>$A$16*I18</f>
+        <f t="shared" si="3"/>
         <v>0.63420223660534913</v>
       </c>
       <c r="K18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6.3420223660534919E-4</v>
       </c>
-      <c r="L18" s="6">
-        <f>G18/(K18*$A$10)</f>
+      <c r="L18">
+        <f t="shared" si="5"/>
         <v>27.869318262687234</v>
       </c>
-      <c r="M18" s="6">
-        <f t="shared" si="3"/>
+      <c r="M18">
+        <f t="shared" si="6"/>
         <v>1596.7943143588461</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A19" s="13">
+      <c r="A19" s="6">
         <v>0.161778534607113</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="4">
         <v>3</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19">
         <f>Metingen!E19-Metingen!F19</f>
         <v>1.9000000000000128E-2</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19">
         <f t="shared" si="0"/>
         <v>9.5000000000000639E-3</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19">
         <f>Metingen!D19</f>
         <v>1.2729999999999999</v>
       </c>
-      <c r="G19" s="6">
-        <f>E19/(2*F19)</f>
+      <c r="G19">
+        <f t="shared" si="1"/>
         <v>3.7313432835821151E-3</v>
       </c>
-      <c r="H19" s="6">
-        <f t="shared" si="1"/>
+      <c r="H19">
+        <f t="shared" si="2"/>
         <v>0.21379022206374149</v>
       </c>
       <c r="I19">
@@ -3449,45 +3750,45 @@
         <v>0.78247261345852892</v>
       </c>
       <c r="J19">
-        <f>$A$16*I19</f>
+        <f t="shared" si="3"/>
         <v>0.63293636387759389</v>
       </c>
       <c r="K19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6.3293636387759392E-4</v>
       </c>
-      <c r="L19" s="6">
-        <f>G19/(K19*$A$10)</f>
+      <c r="L19">
+        <f t="shared" si="5"/>
         <v>29.47644894916904</v>
       </c>
-      <c r="M19" s="6">
-        <f t="shared" si="3"/>
+      <c r="M19">
+        <f t="shared" si="6"/>
         <v>1688.8761198202164</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A20" s="11"/>
-      <c r="C20" s="8">
+      <c r="A20" s="6"/>
+      <c r="C20" s="4">
         <v>4</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20">
         <f>Metingen!E20-Metingen!F20</f>
         <v>1.9000000000000128E-2</v>
       </c>
-      <c r="E20" s="6">
-        <f>D20/2</f>
+      <c r="E20">
+        <f t="shared" si="0"/>
         <v>9.5000000000000639E-3</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20">
         <f>Metingen!D20</f>
         <v>1.2749999999999999</v>
       </c>
-      <c r="G20" s="6">
-        <f>E20/(2*F20)</f>
+      <c r="G20">
+        <f t="shared" si="1"/>
         <v>3.7254901960784566E-3</v>
       </c>
-      <c r="H20" s="6">
-        <f t="shared" si="1"/>
+      <c r="H20">
+        <f t="shared" si="2"/>
         <v>0.21345486485266107</v>
       </c>
       <c r="I20">
@@ -3495,100 +3796,100 @@
         <v>0.78247261345852892</v>
       </c>
       <c r="J20">
-        <f>$A$16*I20</f>
+        <f t="shared" si="3"/>
         <v>0.63293636387759389</v>
       </c>
       <c r="K20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6.3293636387759392E-4</v>
       </c>
-      <c r="L20" s="6">
-        <f>G20/(K20*$A$10)</f>
+      <c r="L20">
+        <f t="shared" si="5"/>
         <v>29.430211382189949</v>
       </c>
-      <c r="M20" s="6">
-        <f t="shared" si="3"/>
+      <c r="M20">
+        <f t="shared" si="6"/>
         <v>1686.2269023773611</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="16">
+      <c r="A21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="2">
         <v>5</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="3">
         <f>Metingen!E21-Metingen!F21</f>
         <v>1.3000000000000123E-2</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="3">
         <f t="shared" si="0"/>
         <v>6.5000000000000613E-3</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="3">
         <f>Metingen!D21</f>
         <v>1.2729999999999999</v>
       </c>
-      <c r="G21" s="15">
-        <f>E21/(2*F21)</f>
+      <c r="G21" s="3">
+        <f t="shared" si="1"/>
         <v>2.5530243519246119E-3</v>
       </c>
-      <c r="H21" s="15">
-        <f t="shared" si="1"/>
+      <c r="H21" s="3">
+        <f t="shared" si="2"/>
         <v>0.14627752035940245</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I21" s="3">
         <f>Metingen!C21/$A$4</f>
         <v>0.40845070422535212</v>
       </c>
-      <c r="J21" s="4">
-        <f>$A$16*I21</f>
+      <c r="J21" s="3">
+        <f t="shared" si="3"/>
         <v>0.33039278194410404</v>
       </c>
-      <c r="K21" s="4">
-        <f t="shared" si="2"/>
+      <c r="K21" s="3">
+        <f t="shared" si="4"/>
         <v>3.3039278194410408E-4</v>
       </c>
-      <c r="L21" s="15">
-        <f>G21/(K21*$A$10)</f>
+      <c r="L21" s="3">
+        <f t="shared" si="5"/>
         <v>38.636200477838123</v>
       </c>
-      <c r="M21" s="15">
-        <f t="shared" si="3"/>
+      <c r="M21" s="3">
+        <f t="shared" si="6"/>
         <v>2213.6912238014593</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A22" s="13">
+      <c r="A22" s="6">
         <f>$A$19*(10^(-3))</f>
         <v>1.6177853460711301E-4</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="8">
-        <v>1</v>
-      </c>
-      <c r="D22" s="6">
+        <v>38</v>
+      </c>
+      <c r="C22" s="4">
+        <v>1</v>
+      </c>
+      <c r="D22">
         <f>Metingen!E22-Metingen!F22</f>
         <v>1.1999999999999789E-2</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22">
         <f t="shared" si="0"/>
         <v>5.9999999999998943E-3</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22">
         <f>Metingen!D22</f>
         <v>1.2509999999999999</v>
       </c>
-      <c r="G22" s="6">
-        <f>E22/(2*F22)</f>
+      <c r="G22">
+        <f t="shared" si="1"/>
         <v>2.39808153477214E-3</v>
       </c>
-      <c r="H22" s="6">
-        <f t="shared" si="1"/>
+      <c r="H22">
+        <f t="shared" si="2"/>
         <v>0.13739995087069859</v>
       </c>
       <c r="I22">
@@ -3596,45 +3897,45 @@
         <v>0.47730829420970267</v>
       </c>
       <c r="J22">
-        <f>$A$16*I22</f>
+        <f t="shared" si="3"/>
         <v>0.38609118196533226</v>
       </c>
       <c r="K22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.8609118196533226E-4</v>
       </c>
-      <c r="L22" s="6">
-        <f>G22/(K22*$A$10)</f>
+      <c r="L22">
+        <f t="shared" si="5"/>
         <v>31.055896207796156</v>
       </c>
-      <c r="M22" s="6">
-        <f t="shared" si="3"/>
+      <c r="M22">
+        <f t="shared" si="6"/>
         <v>1779.3717817030579</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A23" s="11"/>
-      <c r="C23" s="8">
+      <c r="A23" s="6"/>
+      <c r="C23" s="4">
         <v>2</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23">
         <f>Metingen!E23-Metingen!F23</f>
         <v>1.3000000000000123E-2</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23">
         <f t="shared" si="0"/>
         <v>6.5000000000000613E-3</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23">
         <f>Metingen!D23</f>
         <v>1.2589999999999999</v>
       </c>
-      <c r="G23" s="6">
-        <f>E23/(2*F23)</f>
+      <c r="G23">
+        <f t="shared" si="1"/>
         <v>2.5814138204924789E-3</v>
       </c>
-      <c r="H23" s="6">
-        <f t="shared" si="1"/>
+      <c r="H23">
+        <f t="shared" si="2"/>
         <v>0.14790411709096055</v>
       </c>
       <c r="I23">
@@ -3642,47 +3943,47 @@
         <v>0.47417840375586856</v>
       </c>
       <c r="J23">
-        <f>$A$16*I23</f>
+        <f t="shared" si="3"/>
         <v>0.38355943650982194</v>
       </c>
       <c r="K23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.8355943650982195E-4</v>
       </c>
-      <c r="L23" s="6">
-        <f>G23/(K23*$A$10)</f>
+      <c r="L23">
+        <f t="shared" si="5"/>
         <v>33.650766671026425</v>
       </c>
-      <c r="M23" s="6">
-        <f t="shared" si="3"/>
+      <c r="M23">
+        <f t="shared" si="6"/>
         <v>1928.0469076293093</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="4">
         <v>3</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24">
         <f>Metingen!E24-Metingen!F24</f>
         <v>1.0999999999999899E-2</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24">
         <f t="shared" si="0"/>
         <v>5.4999999999999494E-3</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24">
         <f>Metingen!D24</f>
         <v>1.2749999999999999</v>
       </c>
-      <c r="G24" s="6">
-        <f>E24/(2*F24)</f>
+      <c r="G24">
+        <f t="shared" si="1"/>
         <v>2.1568627450980196E-3</v>
       </c>
-      <c r="H24" s="6">
-        <f t="shared" si="1"/>
+      <c r="H24">
+        <f t="shared" si="2"/>
         <v>0.12357913228311762</v>
       </c>
       <c r="I24">
@@ -3690,47 +3991,47 @@
         <v>0.46948356807511737</v>
       </c>
       <c r="J24">
-        <f>$A$16*I24</f>
+        <f t="shared" si="3"/>
         <v>0.37976181832655637</v>
       </c>
       <c r="K24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.7976181832655636E-4</v>
       </c>
-      <c r="L24" s="6">
-        <f>G24/(K24*$A$10)</f>
+      <c r="L24">
+        <f t="shared" si="5"/>
         <v>28.39757238632318</v>
       </c>
-      <c r="M24" s="6">
-        <f t="shared" si="3"/>
+      <c r="M24">
+        <f t="shared" si="6"/>
         <v>1627.0610461535678</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A25" s="11">
+      <c r="A25" s="6">
         <v>635</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="4">
         <v>4</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25">
         <f>Metingen!E25-Metingen!F25</f>
         <v>1.2000000000000011E-2</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25">
         <f t="shared" si="0"/>
         <v>6.0000000000000053E-3</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25">
         <f>Metingen!D25</f>
         <v>1.2649999999999999</v>
       </c>
-      <c r="G25" s="6">
-        <f>E25/(2*F25)</f>
+      <c r="G25">
+        <f t="shared" si="1"/>
         <v>2.3715415019762869E-3</v>
       </c>
-      <c r="H25" s="6">
-        <f t="shared" si="1"/>
+      <c r="H25">
+        <f t="shared" si="2"/>
         <v>0.13587931900335742</v>
       </c>
       <c r="I25">
@@ -3738,45 +4039,45 @@
         <v>0.46948356807511737</v>
       </c>
       <c r="J25">
-        <f>$A$16*I25</f>
+        <f t="shared" si="3"/>
         <v>0.37976181832655637</v>
       </c>
       <c r="K25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.7976181832655636E-4</v>
       </c>
-      <c r="L25" s="6">
-        <f>G25/(K25*$A$10)</f>
+      <c r="L25">
+        <f t="shared" si="5"/>
         <v>31.224064499514842</v>
       </c>
-      <c r="M25" s="6">
-        <f t="shared" si="3"/>
+      <c r="M25">
+        <f t="shared" si="6"/>
         <v>1789.0071150664635</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A26" s="11"/>
-      <c r="C26" s="8">
+      <c r="A26" s="6"/>
+      <c r="C26" s="4">
         <v>5</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26">
         <f>Metingen!E26-Metingen!F26</f>
         <v>1.0999999999999899E-2</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26">
         <f t="shared" si="0"/>
         <v>5.4999999999999494E-3</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26">
         <f>Metingen!D26</f>
         <v>1.2509999999999999</v>
       </c>
-      <c r="G26" s="6">
-        <f>E26/(2*F26)</f>
+      <c r="G26">
+        <f t="shared" si="1"/>
         <v>2.1982414068744804E-3</v>
       </c>
-      <c r="H26" s="6">
-        <f t="shared" si="1"/>
+      <c r="H26">
+        <f t="shared" si="2"/>
         <v>0.12594995496480813</v>
       </c>
       <c r="I26">
@@ -3784,324 +4085,2044 @@
         <v>0.3129890453834116</v>
       </c>
       <c r="J26">
-        <f>$A$16*I26</f>
+        <f t="shared" si="3"/>
         <v>0.25317454555103758</v>
       </c>
       <c r="K26">
+        <f t="shared" si="4"/>
+        <v>2.5317454555103756E-4</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="5"/>
+        <v>43.41355490714875</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="6"/>
+        <v>2487.4134698390881</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A27" s="8"/>
+      <c r="Q27" s="9"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A28" s="8"/>
+      <c r="Q28" s="9"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A29" s="8"/>
+      <c r="Q29" s="9"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A30" s="8"/>
+      <c r="Q30" s="9"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A31" s="8"/>
+      <c r="Q31" s="9"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A32" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:W32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="32.1640625" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" customWidth="1"/>
+    <col min="6" max="6" width="9.1640625" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="8" max="8" width="8" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" customWidth="1"/>
+    <col min="10" max="10" width="8" customWidth="1"/>
+    <col min="11" max="11" width="7.83203125" customWidth="1"/>
+    <col min="12" max="13" width="8.33203125" customWidth="1"/>
+    <col min="14" max="14" width="19.5" customWidth="1"/>
+    <col min="15" max="16" width="16.6640625" customWidth="1"/>
+    <col min="17" max="17" width="19" customWidth="1"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="17.6640625" customWidth="1"/>
+    <col min="20" max="20" width="20.1640625" customWidth="1"/>
+    <col min="21" max="21" width="18" customWidth="1"/>
+    <col min="22" max="22" width="17.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="T1" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A2" s="6"/>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <f>Metingen!F2 / Metingen!G2</f>
+        <v>0.49602227525855219</v>
+      </c>
+      <c r="E2">
+        <f>D2 * $A$28 * ( 1 / Metingen!F2+ 1 / Metingen!G2)</f>
+        <v>5.9507648180531119E-4</v>
+      </c>
+      <c r="F2">
+        <f>Metingen!E2 / Metingen!G2</f>
+        <v>0.50278440731901353</v>
+      </c>
+      <c r="G2">
+        <f>F2 * $A$28 * (1 / Metingen!E2 + 1 / Metingen!G2)</f>
+        <v>5.9776627180549468E-4</v>
+      </c>
+      <c r="H2">
+        <f t="shared" ref="H2:H26" si="0">ACOS(SQRT(D2))</f>
+        <v>0.78937593009791152</v>
+      </c>
+      <c r="I2">
+        <f t="shared" ref="I2:I26" si="1">E2 / SIN(2 * H2)</f>
+        <v>5.950953136494414E-4</v>
+      </c>
+      <c r="J2">
+        <f t="shared" ref="J2:J26" si="2">ACOS(SQRT(F2))</f>
+        <v>0.78261374168670139</v>
+      </c>
+      <c r="K2">
+        <f t="shared" ref="K2:K26" si="3">G2 / SIN(2 * J2)</f>
+        <v>5.9777554089417433E-4</v>
+      </c>
+      <c r="L2">
+        <f t="shared" ref="L2:L26" si="4">(H2 - J2) / 2</f>
+        <v>3.3810942056050619E-3</v>
+      </c>
+      <c r="M2">
+        <f t="shared" ref="M2:M26" si="5">I2 + K2</f>
+        <v>1.1928708545436157E-3</v>
+      </c>
+      <c r="N2">
+        <f>Metingen!C2/$A$4</f>
+        <v>1.0031298904538339</v>
+      </c>
+      <c r="O2">
+        <f t="shared" ref="O2:O26" si="6">$A$16*N2</f>
+        <v>0.81142441849107527</v>
+      </c>
+      <c r="P2">
+        <v>1E-3</v>
+      </c>
+      <c r="Q2">
+        <f t="shared" ref="Q2:Q26" si="7">L2 / (A$19 * N2)</f>
+        <v>2.0834313884049386E-2</v>
+      </c>
+      <c r="R2">
+        <f>Q2*((M2/L2)+(P2/O2)+($A$13/$A$7))</f>
+        <v>7.4803220157331433E-3</v>
+      </c>
+      <c r="S2">
+        <f>R2/Q2</f>
+        <v>0.35903855809046004</v>
+      </c>
+      <c r="T2">
+        <f>S2*100</f>
+        <v>35.903855809046007</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="4">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <f>Metingen!F3 / Metingen!G3</f>
+        <v>0.49503377036154156</v>
+      </c>
+      <c r="E3">
+        <f>D3 * $A$28 * ( 1 / Metingen!F3+ 1 / Metingen!G3)</f>
+        <v>5.9397448166926571E-4</v>
+      </c>
+      <c r="F3">
+        <f>Metingen!E3 / Metingen!G3</f>
+        <v>0.50297973778307514</v>
+      </c>
+      <c r="G3">
+        <f>F3 * $A$28 * (1 / Metingen!E3 + 1 / Metingen!G3)</f>
+        <v>5.9713140158246941E-4</v>
+      </c>
+      <c r="H3">
+        <f t="shared" si="0"/>
+        <v>0.7903644746957259</v>
+      </c>
+      <c r="I3">
+        <f t="shared" si="1"/>
+        <v>5.9400378274148389E-4</v>
+      </c>
+      <c r="J3">
         <f t="shared" si="2"/>
-        <v>2.5317454555103756E-4</v>
-      </c>
-      <c r="L26" s="6">
-        <f>G26/(K26*$A$10)</f>
-        <v>43.41355490714875</v>
-      </c>
-      <c r="M26" s="6">
+        <v>0.78241840797635342</v>
+      </c>
+      <c r="K3">
         <f t="shared" si="3"/>
-        <v>2487.4134698390881</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A27" s="18"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="5"/>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A28" s="18"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="5"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A29" s="18"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
-      <c r="O29" s="6"/>
-      <c r="P29" s="6"/>
-      <c r="Q29" s="5"/>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A30" s="18"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
-      <c r="N30" s="6"/>
-      <c r="O30" s="6"/>
-      <c r="P30" s="6"/>
-      <c r="Q30" s="5"/>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A31" s="18"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6"/>
-      <c r="O31" s="6"/>
-      <c r="P31" s="6"/>
-      <c r="Q31" s="5"/>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A32" s="18"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="6"/>
-      <c r="N32" s="6"/>
-      <c r="O32" s="6"/>
-      <c r="P32" s="6"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A33" s="17"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="6"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A34" s="17"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="6"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="6"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A35" s="17"/>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A36" s="17"/>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A37" s="17"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A38" s="17"/>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A39" s="17"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A40" s="17"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A41" s="17"/>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A42" s="17"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A43" s="17"/>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A44" s="17"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A45" s="17"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A46" s="17"/>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A47" s="17"/>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A48" s="17"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" s="17"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A50" s="17"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A51" s="17"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A52" s="17"/>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A53" s="17"/>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A54" s="17"/>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A55" s="17"/>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A56" s="17"/>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A57" s="17"/>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A58" s="17"/>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A59" s="17"/>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A60" s="17"/>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A61" s="17"/>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A62" s="17"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A63" s="17"/>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A64" s="17"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A65" s="17"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A66" s="17"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A67" s="17"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A68" s="17"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A69" s="17"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A70" s="17"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A71" s="17"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A72" s="17"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A73" s="17"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A74" s="17"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A75" s="17"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A76" s="17"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A77" s="17"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A78" s="17"/>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A79" s="17"/>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A80" s="17"/>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A81" s="17"/>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A82" s="17"/>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A83" s="17"/>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A84" s="17"/>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A85" s="17"/>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A86" s="17"/>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A87" s="17"/>
+        <v>5.9714200552999242E-4</v>
+      </c>
+      <c r="L3">
+        <f t="shared" si="4"/>
+        <v>3.9730333596862399E-3</v>
+      </c>
+      <c r="M3">
+        <f t="shared" si="5"/>
+        <v>1.1911457882714763E-3</v>
+      </c>
+      <c r="N3">
+        <f>Metingen!C3/$A$4</f>
+        <v>1.0125195618153364</v>
+      </c>
+      <c r="O3">
+        <f t="shared" si="6"/>
+        <v>0.81901965485760642</v>
+      </c>
+      <c r="P3">
+        <v>1E-3</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" si="7"/>
+        <v>2.4254810834649539E-2</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R26" si="8">Q3*((M3/L3)+(P3/O3)+($A$13/$A$7))</f>
+        <v>7.4226662939378745E-3</v>
+      </c>
+      <c r="S3">
+        <f t="shared" ref="S3:S26" si="9">R3/Q3</f>
+        <v>0.30602862024114919</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T26" si="10">S3*100</f>
+        <v>30.60286202411492</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
+        <v>63.9</v>
+      </c>
+      <c r="C4" s="4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <f>Metingen!F4 / Metingen!G4</f>
+        <v>0.4924543288324067</v>
+      </c>
+      <c r="E4">
+        <f>D4 * $A$28 * ( 1 / Metingen!F4+ 1 / Metingen!G4)</f>
+        <v>5.9271418936950244E-4</v>
+      </c>
+      <c r="F4">
+        <f>Metingen!E4 / Metingen!G4</f>
+        <v>0.50039714058776807</v>
+      </c>
+      <c r="G4">
+        <f>F4 * $A$28 * (1 / Metingen!E4 + 1 / Metingen!G4)</f>
+        <v>5.9586860229855765E-4</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>0.79294412101375744</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="1"/>
+        <v>5.9278169581800512E-4</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="2"/>
+        <v>0.78500102276792205</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="3"/>
+        <v>5.9586879026020888E-4</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="4"/>
+        <v>3.9715491229176947E-3</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="5"/>
+        <v>1.188650486078214E-3</v>
+      </c>
+      <c r="N4">
+        <f>Metingen!C4/$A$4</f>
+        <v>1.0031298904538339</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="6"/>
+        <v>0.81142441849107527</v>
+      </c>
+      <c r="P4">
+        <v>1E-3</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="7"/>
+        <v>2.447269907345891E-2</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="8"/>
+        <v>7.4769919653387921E-3</v>
+      </c>
+      <c r="S4">
+        <f t="shared" si="9"/>
+        <v>0.30552379788168632</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="10"/>
+        <v>30.552379788168633</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A5" s="4"/>
+      <c r="C5" s="4">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <f>Metingen!F5 / Metingen!G5</f>
+        <v>0.49781659388646288</v>
+      </c>
+      <c r="E5">
+        <f>D5 * $A$28 * ( 1 / Metingen!F5+ 1 / Metingen!G5)</f>
+        <v>5.9460761964528108E-4</v>
+      </c>
+      <c r="F5">
+        <f>Metingen!E5 / Metingen!G5</f>
+        <v>0.50774116712981332</v>
+      </c>
+      <c r="G5">
+        <f>F5 * $A$28 * (1 / Metingen!E5 + 1 / Metingen!G5)</f>
+        <v>5.9854750580778612E-4</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>0.78758157645029137</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="1"/>
+        <v>5.9461328902728878E-4</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="2"/>
+        <v>0.77765668697119417</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="3"/>
+        <v>5.9861925542584226E-4</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="4"/>
+        <v>4.9624447395485993E-3</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="5"/>
+        <v>1.193232544453131E-3</v>
+      </c>
+      <c r="N5">
+        <f>Metingen!C5/$A$4</f>
+        <v>1.0015649452269171</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="6"/>
+        <v>0.81015854576332025</v>
+      </c>
+      <c r="P5">
+        <v>1E-3</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="7"/>
+        <v>3.062638026531617E-2</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="8"/>
+        <v>7.5551264046134405E-3</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="9"/>
+        <v>0.24668688689826943</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="10"/>
+        <v>24.668688689826944</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="2">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <f>Metingen!F6 / Metingen!G6</f>
+        <v>0.49484126984126986</v>
+      </c>
+      <c r="E6">
+        <f>D6 * $A$28 * ( 1 / Metingen!F6+ 1 / Metingen!G6)</f>
+        <v>5.9319098009574193E-4</v>
+      </c>
+      <c r="F6">
+        <f>Metingen!E6 / Metingen!G6</f>
+        <v>0.50476190476190474</v>
+      </c>
+      <c r="G6">
+        <f>F6 * $A$28 * (1 / Metingen!E6 + 1 / Metingen!G6)</f>
+        <v>5.9712773998488286E-4</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>0.79055698508502292</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="1"/>
+        <v>5.932225552028208E-4</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="2"/>
+        <v>0.78063618664613843</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="3"/>
+        <v>5.9715482245036988E-4</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="4"/>
+        <v>4.9603992194422464E-3</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="5"/>
+        <v>1.1903773776531907E-3</v>
+      </c>
+      <c r="N6" s="3">
+        <f>Metingen!C6/$A$4</f>
+        <v>0.77464788732394363</v>
+      </c>
+      <c r="O6" s="3">
+        <f t="shared" si="6"/>
+        <v>0.62660700023881788</v>
+      </c>
+      <c r="P6">
+        <v>1E-3</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="7"/>
+        <v>3.9581421988197509E-2</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="8"/>
+        <v>9.7596711948788033E-3</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="9"/>
+        <v>0.24657202052490604</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="10"/>
+        <v>24.657202052490604</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
+        <v>200</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <f>Metingen!F7 / Metingen!G7</f>
+        <v>0.49244232299124902</v>
+      </c>
+      <c r="E7">
+        <f>D7 * $A$28 * ( 1 / Metingen!F7+ 1 / Metingen!G7)</f>
+        <v>5.9365247533462579E-4</v>
+      </c>
+      <c r="F7">
+        <f>Metingen!E7 / Metingen!G7</f>
+        <v>0.49960222752585526</v>
+      </c>
+      <c r="G7">
+        <f>F7 * $A$28 * (1 / Metingen!E7 + 1 / Metingen!G7)</f>
+        <v>5.9650048827599659E-4</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>0.7929561282244828</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="1"/>
+        <v>5.9372030401383922E-4</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="2"/>
+        <v>0.78579593591355079</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="3"/>
+        <v>5.9650067703620956E-4</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="4"/>
+        <v>3.580096155466006E-3</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="5"/>
+        <v>1.1902209810500488E-3</v>
+      </c>
+      <c r="N7">
+        <f>Metingen!C7/$A$4</f>
+        <v>0.90140845070422537</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="6"/>
+        <v>0.72914269118698816</v>
+      </c>
+      <c r="P7">
+        <v>1E-3</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="7"/>
+        <v>2.4550038001737939E-2</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="8"/>
+        <v>8.3182035840817705E-3</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="9"/>
+        <v>0.33882650542100629</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="10"/>
+        <v>33.882650542100627</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A8" s="6"/>
+      <c r="C8" s="4">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <f>Metingen!F8 / Metingen!G8</f>
+        <v>0.4948289578361178</v>
+      </c>
+      <c r="E8">
+        <f>D8 * $A$28 * ( 1 / Metingen!F8+ 1 / Metingen!G8)</f>
+        <v>5.9460181298174935E-4</v>
+      </c>
+      <c r="F8">
+        <f>Metingen!E8 / Metingen!G8</f>
+        <v>0.50198886237072404</v>
+      </c>
+      <c r="G8">
+        <f>F8 * $A$28 * (1 / Metingen!E8 + 1 / Metingen!G8)</f>
+        <v>5.9744982592312027E-4</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>0.79056929774709928</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="1"/>
+        <v>5.9463361445377292E-4</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="2"/>
+        <v>0.78340929578195928</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="3"/>
+        <v>5.9745455249264265E-4</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="4"/>
+        <v>3.5800009825699974E-3</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="5"/>
+        <v>1.1920881669464155E-3</v>
+      </c>
+      <c r="N8">
+        <f>Metingen!C8/$A$4</f>
+        <v>0.89827856025039121</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="6"/>
+        <v>0.72661094573147778</v>
+      </c>
+      <c r="P8">
+        <v>1E-3</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="7"/>
+        <v>2.4634923294239792E-2</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="8"/>
+        <v>8.3601490154752676E-3</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="9"/>
+        <v>0.33936168242220838</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="10"/>
+        <v>33.936168242220837</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="4">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <f>Metingen!F9 / Metingen!G9</f>
+        <v>0.49085123309466988</v>
+      </c>
+      <c r="E9">
+        <f>D9 * $A$28 * ( 1 / Metingen!F9+ 1 / Metingen!G9)</f>
+        <v>5.9301958356987674E-4</v>
+      </c>
+      <c r="F9">
+        <f>Metingen!E9 / Metingen!G9</f>
+        <v>0.49880668257756566</v>
+      </c>
+      <c r="G9">
+        <f>F9 * $A$28 * (1 / Metingen!E9 + 1 / Metingen!G9)</f>
+        <v>5.9618404239362207E-4</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>0.79454744088050799</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="1"/>
+        <v>5.931188799061138E-4</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="2"/>
+        <v>0.78659148195274664</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="3"/>
+        <v>5.9618574034074395E-4</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="4"/>
+        <v>3.9779794638806765E-3</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="5"/>
+        <v>1.1893046202468577E-3</v>
+      </c>
+      <c r="N9">
+        <f>Metingen!C9/$A$4</f>
+        <v>0.9061032863849765</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="6"/>
+        <v>0.73294030937025367</v>
+      </c>
+      <c r="P9">
+        <v>1E-3</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="7"/>
+        <v>2.713713117578823E-2</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="8"/>
+        <v>8.2859540420489944E-3</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="9"/>
+        <v>0.30533640377733551</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="10"/>
+        <v>30.533640377733551</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="C10" s="4">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <f>Metingen!F10 / Metingen!G10</f>
+        <v>0.49045346062052514</v>
+      </c>
+      <c r="E10">
+        <f>D10 * $A$28 * ( 1 / Metingen!F10+ 1 / Metingen!G10)</f>
+        <v>5.9286136062868943E-4</v>
+      </c>
+      <c r="F10">
+        <f>Metingen!E10 / Metingen!G10</f>
+        <v>0.49840891010342087</v>
+      </c>
+      <c r="G10">
+        <f>F10 * $A$28 * (1 / Metingen!E10 + 1 / Metingen!G10)</f>
+        <v>5.9602581945243486E-4</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>0.79494528289700506</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="1"/>
+        <v>5.9296945269991927E-4</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="2"/>
+        <v>0.78698925597934011</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="3"/>
+        <v>5.960288372340157E-4</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="4"/>
+        <v>3.9780134588324745E-3</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="5"/>
+        <v>1.1889982899339351E-3</v>
+      </c>
+      <c r="N10">
+        <f>Metingen!C10/$A$4</f>
+        <v>0.90453834115805942</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="6"/>
+        <v>0.73167443664249854</v>
+      </c>
+      <c r="P10">
+        <v>1E-3</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="7"/>
+        <v>2.7184313539002053E-2</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="8"/>
+        <v>8.2982618984762078E-3</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="9"/>
+        <v>0.30525920349507712</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="10"/>
+        <v>30.525920349507711</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A11" s="4"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="2">
+        <v>5</v>
+      </c>
+      <c r="D11">
+        <f>Metingen!F11 / Metingen!G11</f>
+        <v>0.49443118536197306</v>
+      </c>
+      <c r="E11">
+        <f>D11 * $A$28 * ( 1 / Metingen!F11+ 1 / Metingen!G11)</f>
+        <v>5.9444359004056215E-4</v>
+      </c>
+      <c r="F11">
+        <f>Metingen!E11 / Metingen!G11</f>
+        <v>0.50119331742243445</v>
+      </c>
+      <c r="G11">
+        <f>F11 * $A$28 * (1 / Metingen!E11 + 1 / Metingen!G11)</f>
+        <v>5.9713338004074585E-4</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>0.79096709317416192</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="1"/>
+        <v>5.9448046287943442E-4</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="2"/>
+        <v>0.78420484484214981</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="3"/>
+        <v>5.9713508069160514E-4</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="4"/>
+        <v>3.3811241660060554E-3</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="5"/>
+        <v>1.1916155435710396E-3</v>
+      </c>
+      <c r="N11" s="3">
+        <f>Metingen!C11/$A$4</f>
+        <v>0.65571205007824729</v>
+      </c>
+      <c r="O11" s="3">
+        <f t="shared" si="6"/>
+        <v>0.53040067292942372</v>
+      </c>
+      <c r="P11">
+        <v>1E-3</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="7"/>
+        <v>3.1873302001409372E-2</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="8"/>
+        <v>1.1452623335594905E-2</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="9"/>
+        <v>0.35931712801794097</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="10"/>
+        <v>35.931712801794099</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <f>Metingen!F12 / Metingen!G12</f>
+        <v>0.49721559268098653</v>
+      </c>
+      <c r="E12">
+        <f>D12 * $A$28 * ( 1 / Metingen!F12+ 1 / Metingen!G12)</f>
+        <v>5.9555115062887303E-4</v>
+      </c>
+      <c r="F12">
+        <f>Metingen!E12 / Metingen!G12</f>
+        <v>0.50556881463802705</v>
+      </c>
+      <c r="G12">
+        <f>F12 * $A$28 * (1 / Metingen!E12 + 1 / Metingen!G12)</f>
+        <v>5.9887383239380556E-4</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>0.78818258510819506</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="1"/>
+        <v>5.9556038536942091E-4</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="2"/>
+        <v>0.77982923362073442</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="3"/>
+        <v>5.989109800369069E-4</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="4"/>
+        <v>4.1766757437303181E-3</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="5"/>
+        <v>1.1944713654063279E-3</v>
+      </c>
+      <c r="N12">
+        <f>Metingen!C12/$A$4</f>
+        <v>1.2097026604068857</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="6"/>
+        <v>0.97851961855476011</v>
+      </c>
+      <c r="P12">
+        <v>1E-3</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="7"/>
+        <v>2.1341808914874517E-2</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="8"/>
+        <v>6.2319808554748037E-3</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="9"/>
+        <v>0.29200808986399107</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="10"/>
+        <v>29.200808986399107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <f>Metingen!F13 / Metingen!G13</f>
+        <v>0.50079554494828959</v>
+      </c>
+      <c r="E13">
+        <f>D13 * $A$28 * ( 1 / Metingen!F13+ 1 / Metingen!G13)</f>
+        <v>5.9697515709955832E-4</v>
+      </c>
+      <c r="F13">
+        <f>Metingen!E13 / Metingen!G13</f>
+        <v>0.50954653937947492</v>
+      </c>
+      <c r="G13">
+        <f>F13 * $A$28 * (1 / Metingen!E13 + 1 / Metingen!G13)</f>
+        <v>6.0045606180567828E-4</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>0.78460261811349563</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="1"/>
+        <v>5.9697591274231437E-4</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="2"/>
+        <v>0.77585104389789128</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="3"/>
+        <v>6.0056553856316895E-4</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="4"/>
+        <v>4.3757871078021759E-3</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="5"/>
+        <v>1.1975414513054833E-3</v>
+      </c>
+      <c r="N13">
+        <f>Metingen!C13/$A$4</f>
+        <v>1.2065727699530515</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="6"/>
+        <v>0.97598787309924973</v>
+      </c>
+      <c r="P13">
+        <v>1E-3</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="7"/>
+        <v>2.2417220686907015E-2</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="8"/>
+        <v>6.2700770404829353E-3</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="9"/>
+        <v>0.27969912631252419</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="10"/>
+        <v>27.96991263125242</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A14" s="6"/>
+      <c r="C14" s="4">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <f>Metingen!F14 / Metingen!G14</f>
+        <v>0.50119331742243445</v>
+      </c>
+      <c r="E14">
+        <f>D14 * $A$28 * ( 1 / Metingen!F14+ 1 / Metingen!G14)</f>
+        <v>5.9713338004074585E-4</v>
+      </c>
+      <c r="F14">
+        <f>Metingen!E14 / Metingen!G14</f>
+        <v>0.51034208432776451</v>
+      </c>
+      <c r="G14">
+        <f>F14 * $A$28 * (1 / Metingen!E14 + 1 / Metingen!G14)</f>
+        <v>6.0077250768805269E-4</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>0.78420484484214981</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="1"/>
+        <v>5.9713508069160514E-4</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="2"/>
+        <v>0.77505534147701582</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="3"/>
+        <v>6.0090106464312119E-4</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="4"/>
+        <v>4.5747516825669909E-3</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="5"/>
+        <v>1.1980361453347264E-3</v>
+      </c>
+      <c r="N14">
+        <f>Metingen!C14/$A$4</f>
+        <v>1.2065727699530515</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="6"/>
+        <v>0.97598787309924973</v>
+      </c>
+      <c r="P14">
+        <v>1E-3</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="7"/>
+        <v>2.3436519083171937E-2</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="8"/>
+        <v>6.278752233223512E-3</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="9"/>
+        <v>0.26790464108348871</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="10"/>
+        <v>26.790464108348871</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="4">
+        <v>4</v>
+      </c>
+      <c r="D15">
+        <f>Metingen!F15 / Metingen!G15</f>
+        <v>0.49363564041368346</v>
+      </c>
+      <c r="E15">
+        <f>D15 * $A$28 * ( 1 / Metingen!F15+ 1 / Metingen!G15)</f>
+        <v>5.9412714415818752E-4</v>
+      </c>
+      <c r="F15">
+        <f>Metingen!E15 / Metingen!G15</f>
+        <v>0.50517104216388231</v>
+      </c>
+      <c r="G15">
+        <f>F15 * $A$28 * (1 / Metingen!E15 + 1 / Metingen!G15)</f>
+        <v>5.9871560945261824E-4</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>0.79176269485552897</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="1"/>
+        <v>5.9417528033416859E-4</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="2"/>
+        <v>0.78022702904779728</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="3"/>
+        <v>5.9874763094547008E-4</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="4"/>
+        <v>5.7678329038658438E-3</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="5"/>
+        <v>1.1929229112796387E-3</v>
+      </c>
+      <c r="N15">
+        <f>Metingen!C15/$A$4</f>
+        <v>1.1987480438184663</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="6"/>
+        <v>0.96965850946047383</v>
+      </c>
+      <c r="P15">
+        <v>1E-3</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="7"/>
+        <v>2.9741568024165096E-2</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="8"/>
+        <v>6.3306327816733607E-3</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="9"/>
+        <v>0.21285470814886781</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="10"/>
+        <v>21.285470814886782</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A16" s="6">
+        <f>(A19/$A$7)*10^(3)</f>
+        <v>0.808892673035565</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="2">
+        <v>5</v>
+      </c>
+      <c r="D16">
+        <f>Metingen!F16 / Metingen!G16</f>
+        <v>0.50556881463802705</v>
+      </c>
+      <c r="E16">
+        <f>D16 * $A$28 * ( 1 / Metingen!F16+ 1 / Metingen!G16)</f>
+        <v>5.9887383239380556E-4</v>
+      </c>
+      <c r="F16">
+        <f>Metingen!E16 / Metingen!G16</f>
+        <v>0.51312649164677815</v>
+      </c>
+      <c r="G16">
+        <f>F16 * $A$28 * (1 / Metingen!E16 + 1 / Metingen!G16)</f>
+        <v>6.0188006827636357E-4</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>0.77982923362073442</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="1"/>
+        <v>5.989109800369069E-4</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="2"/>
+        <v>0.77227016344462807</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="3"/>
+        <v>6.0208758918211679E-4</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="4"/>
+        <v>3.7795350880531764E-3</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="5"/>
+        <v>1.2009985692190237E-3</v>
+      </c>
+      <c r="N16" s="3">
+        <f>Metingen!C16/$A$4</f>
+        <v>0.54460093896713613</v>
+      </c>
+      <c r="O16" s="3">
+        <f t="shared" si="6"/>
+        <v>0.44052370925880535</v>
+      </c>
+      <c r="P16">
+        <v>1E-3</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="7"/>
+        <v>4.2898202850561215E-2</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="8"/>
+        <v>1.3943357183843184E-2</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="9"/>
+        <v>0.3250335971512795</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="10"/>
+        <v>32.503359715127949</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A17" s="6"/>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <f>Metingen!F17 / Metingen!G17</f>
+        <v>0.49642004773269693</v>
+      </c>
+      <c r="E17">
+        <f>D17 * $A$28 * ( 1 / Metingen!F17+ 1 / Metingen!G17)</f>
+        <v>5.952347047464985E-4</v>
+      </c>
+      <c r="F17">
+        <f>Metingen!E17 / Metingen!G17</f>
+        <v>0.50278440731901353</v>
+      </c>
+      <c r="G17">
+        <f>F17 * $A$28 * (1 / Metingen!E17 + 1 / Metingen!G17)</f>
+        <v>5.9776627180549468E-4</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>0.78897814625270812</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="1"/>
+        <v>5.9524996245841262E-4</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="2"/>
+        <v>0.78261374168670139</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="3"/>
+        <v>5.9777554089417433E-4</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="4"/>
+        <v>3.1822022830033658E-3</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="5"/>
+        <v>1.1930255033525869E-3</v>
+      </c>
+      <c r="N17">
+        <f>Metingen!C17/$A$4</f>
+        <v>0.78247261345852892</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="6"/>
+        <v>0.63293636387759389</v>
+      </c>
+      <c r="P17">
+        <v>1E-3</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="7"/>
+        <v>2.5138406201755104E-2</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="8"/>
+        <v>9.5899387781322697E-3</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="9"/>
+        <v>0.38148555247160909</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="10"/>
+        <v>38.148555247160907</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="4">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <f>Metingen!F18 / Metingen!G18</f>
+        <v>0.50238663484486878</v>
+      </c>
+      <c r="E18">
+        <f>D18 * $A$28 * ( 1 / Metingen!F18+ 1 / Metingen!G18)</f>
+        <v>5.9760804886430736E-4</v>
+      </c>
+      <c r="F18">
+        <f>Metingen!E18 / Metingen!G18</f>
+        <v>0.50954653937947492</v>
+      </c>
+      <c r="G18">
+        <f>F18 * $A$28 * (1 / Metingen!E18 + 1 / Metingen!G18)</f>
+        <v>6.0045606180567828E-4</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>0.78301151948959724</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="1"/>
+        <v>5.976148569624731E-4</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="2"/>
+        <v>0.77585104389789128</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="3"/>
+        <v>6.0056553856316895E-4</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="4"/>
+        <v>3.5802377958529807E-3</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="5"/>
+        <v>1.198180395525642E-3</v>
+      </c>
+      <c r="N18">
+        <f>Metingen!C18/$A$4</f>
+        <v>0.784037558685446</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="6"/>
+        <v>0.63420223660534913</v>
+      </c>
+      <c r="P18">
+        <v>1E-3</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="7"/>
+        <v>2.8226310072766971E-2</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="8"/>
+        <v>9.6319973030914736E-3</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="9"/>
+        <v>0.34124181581865787</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="10"/>
+        <v>34.124181581865784</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A19" s="6">
+        <v>0.161778534607113</v>
+      </c>
+      <c r="C19" s="4">
+        <v>3</v>
+      </c>
+      <c r="D19">
+        <f>Metingen!F19 / Metingen!G19</f>
+        <v>0.50238663484486878</v>
+      </c>
+      <c r="E19">
+        <f>D19 * $A$28 * ( 1 / Metingen!F19+ 1 / Metingen!G19)</f>
+        <v>5.9760804886430736E-4</v>
+      </c>
+      <c r="F19">
+        <f>Metingen!E19 / Metingen!G19</f>
+        <v>0.50994431185361977</v>
+      </c>
+      <c r="G19">
+        <f>F19 * $A$28 * (1 / Metingen!E19 + 1 / Metingen!G19)</f>
+        <v>6.0061428474686548E-4</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="0"/>
+        <v>0.78301151948959724</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="1"/>
+        <v>5.976148569624731E-4</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="2"/>
+        <v>0.77545319583615957</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="3"/>
+        <v>6.0073310869760799E-4</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="4"/>
+        <v>3.7791618267188354E-3</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="5"/>
+        <v>1.1983479656600812E-3</v>
+      </c>
+      <c r="N19">
+        <f>Metingen!C19/$A$4</f>
+        <v>0.78247261345852892</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="6"/>
+        <v>0.63293636387759389</v>
+      </c>
+      <c r="P19">
+        <v>1E-3</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="7"/>
+        <v>2.9854200535788012E-2</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="8"/>
+        <v>9.6630142042004354E-3</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="9"/>
+        <v>0.32367352100475116</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="10"/>
+        <v>32.367352100475117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A20" s="6"/>
+      <c r="C20" s="4">
+        <v>4</v>
+      </c>
+      <c r="D20">
+        <f>Metingen!F20 / Metingen!G20</f>
+        <v>0.50397772474144786</v>
+      </c>
+      <c r="E20">
+        <f>D20 * $A$28 * ( 1 / Metingen!F20+ 1 / Metingen!G20)</f>
+        <v>5.9824094062905662E-4</v>
+      </c>
+      <c r="F20">
+        <f>Metingen!E20 / Metingen!G20</f>
+        <v>0.51153540175019896</v>
+      </c>
+      <c r="G20">
+        <f>F20 * $A$28 * (1 / Metingen!E20 + 1 / Metingen!G20)</f>
+        <v>6.0124717651161464E-4</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="0"/>
+        <v>0.78142039669698504</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="1"/>
+        <v>5.9825987261593672E-4</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="2"/>
+        <v>0.77386173809278591</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="3"/>
+        <v>6.0140725092015259E-4</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="4"/>
+        <v>3.7793293020995655E-3</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="5"/>
+        <v>1.1996671235360893E-3</v>
+      </c>
+      <c r="N20">
+        <f>Metingen!C20/$A$4</f>
+        <v>0.78247261345852892</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="6"/>
+        <v>0.63293636387759389</v>
+      </c>
+      <c r="P20">
+        <v>1E-3</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="7"/>
+        <v>2.9855523539096783E-2</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="8"/>
+        <v>9.6734438455429329E-3</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="9"/>
+        <v>0.32400851496960831</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="10"/>
+        <v>32.400851496960833</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="2">
+        <v>5</v>
+      </c>
+      <c r="D21">
+        <f>Metingen!F21 / Metingen!G21</f>
+        <v>0.50397772474144786</v>
+      </c>
+      <c r="E21">
+        <f>D21 * $A$28 * ( 1 / Metingen!F21+ 1 / Metingen!G21)</f>
+        <v>5.9824094062905662E-4</v>
+      </c>
+      <c r="F21">
+        <f>Metingen!E21 / Metingen!G21</f>
+        <v>0.50914876690533017</v>
+      </c>
+      <c r="G21">
+        <f>F21 * $A$28 * (1 / Metingen!E21 + 1 / Metingen!G21)</f>
+        <v>6.0029783886449096E-4</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="0"/>
+        <v>0.78142039669698504</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="1"/>
+        <v>5.9825987261593672E-4</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="2"/>
+        <v>0.77624888591438845</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="3"/>
+        <v>6.0039835388575114E-4</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="4"/>
+        <v>2.5857553912982945E-3</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="5"/>
+        <v>1.1986582265016879E-3</v>
+      </c>
+      <c r="N21" s="3">
+        <f>Metingen!C21/$A$4</f>
+        <v>0.40845070422535212</v>
+      </c>
+      <c r="O21" s="3">
+        <f t="shared" si="6"/>
+        <v>0.33039278194410404</v>
+      </c>
+      <c r="P21">
+        <v>1E-3</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="7"/>
+        <v>3.9131535744866143E-2</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="8"/>
+        <v>1.8453994415856417E-2</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="9"/>
+        <v>0.47158881103401329</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="10"/>
+        <v>47.158881103401328</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A22" s="6">
+        <f>$A$19*(10^(-3))</f>
+        <v>1.6177853460711301E-4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="4">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <f>Metingen!F22 / Metingen!G22</f>
+        <v>0.4952267303102626</v>
+      </c>
+      <c r="E22">
+        <f>D22 * $A$28 * ( 1 / Metingen!F22+ 1 / Metingen!G22)</f>
+        <v>5.9476003592293678E-4</v>
+      </c>
+      <c r="F22">
+        <f>Metingen!E22 / Metingen!G22</f>
+        <v>0.5</v>
+      </c>
+      <c r="G22">
+        <f>F22 * $A$28 * (1 / Metingen!E22 + 1 / Metingen!G22)</f>
+        <v>5.966587112171838E-4</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="0"/>
+        <v>0.79017150559327309</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="1"/>
+        <v>5.9478713992404105E-4</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="2"/>
+        <v>0.78539816339744817</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="3"/>
+        <v>5.966587112171838E-4</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="4"/>
+        <v>2.3866710979124628E-3</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="5"/>
+        <v>1.191445851141225E-3</v>
+      </c>
+      <c r="N22">
+        <f>Metingen!C22/$A$4</f>
+        <v>0.47730829420970267</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="6"/>
+        <v>0.38609118196533226</v>
+      </c>
+      <c r="P22">
+        <v>1E-3</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="7"/>
+        <v>3.0908127527848665E-2</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="8"/>
+        <v>1.56641861901545E-2</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="9"/>
+        <v>0.50679829038626956</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="10"/>
+        <v>50.679829038626956</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A23" s="6"/>
+      <c r="C23" s="4">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <f>Metingen!F23 / Metingen!G23</f>
+        <v>0.49840891010342087</v>
+      </c>
+      <c r="E23">
+        <f>D23 * $A$28 * ( 1 / Metingen!F23+ 1 / Metingen!G23)</f>
+        <v>5.9602581945243486E-4</v>
+      </c>
+      <c r="F23">
+        <f>Metingen!E23 / Metingen!G23</f>
+        <v>0.50357995226730312</v>
+      </c>
+      <c r="G23">
+        <f>F23 * $A$28 * (1 / Metingen!E23 + 1 / Metingen!G23)</f>
+        <v>5.980827176878692E-4</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="0"/>
+        <v>0.78698925597934011</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="1"/>
+        <v>5.960288372340157E-4</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="2"/>
+        <v>0.78181818054218832</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="3"/>
+        <v>5.9809804840318958E-4</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="4"/>
+        <v>2.5855377185758921E-3</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="5"/>
+        <v>1.1941268856372053E-3</v>
+      </c>
+      <c r="N23">
+        <f>Metingen!C23/$A$4</f>
+        <v>0.47417840375586856</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="6"/>
+        <v>0.38355943650982194</v>
+      </c>
+      <c r="P23">
+        <v>1E-3</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="7"/>
+        <v>3.370452493755402E-2</v>
+      </c>
+      <c r="R23">
+        <f t="shared" si="8"/>
+        <v>1.5822782125535239E-2</v>
+      </c>
+      <c r="S23">
+        <f t="shared" si="9"/>
+        <v>0.46945572307726818</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="10"/>
+        <v>46.94557230772682</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A24" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="4">
+        <v>3</v>
+      </c>
+      <c r="D24">
+        <f>Metingen!F24 / Metingen!G24</f>
+        <v>0.50517104216388231</v>
+      </c>
+      <c r="E24">
+        <f>D24 * $A$28 * ( 1 / Metingen!F24+ 1 / Metingen!G24)</f>
+        <v>5.9871560945261824E-4</v>
+      </c>
+      <c r="F24">
+        <f>Metingen!E24 / Metingen!G24</f>
+        <v>0.50954653937947492</v>
+      </c>
+      <c r="G24">
+        <f>F24 * $A$28 * (1 / Metingen!E24 + 1 / Metingen!G24)</f>
+        <v>6.0045606180567828E-4</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="0"/>
+        <v>0.78022702904779728</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="1"/>
+        <v>5.9874763094547008E-4</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="2"/>
+        <v>0.77585104389789128</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="3"/>
+        <v>6.0056553856316895E-4</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="4"/>
+        <v>2.1879925749530016E-3</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="5"/>
+        <v>1.1993131695086389E-3</v>
+      </c>
+      <c r="N24">
+        <f>Metingen!C24/$A$4</f>
+        <v>0.46948356807511737</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="6"/>
+        <v>0.37976181832655637</v>
+      </c>
+      <c r="P24">
+        <v>1E-3</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="7"/>
+        <v>2.8807432308420637E-2</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="8"/>
+        <v>1.6010227465777509E-2</v>
+      </c>
+      <c r="S24">
+        <f t="shared" si="9"/>
+        <v>0.55576725111656666</v>
+      </c>
+      <c r="T24">
+        <f t="shared" si="10"/>
+        <v>55.576725111656664</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A25" s="6">
+        <v>635</v>
+      </c>
+      <c r="C25" s="4">
+        <v>4</v>
+      </c>
+      <c r="D25">
+        <f>Metingen!F25 / Metingen!G25</f>
+        <v>0.50119331742243445</v>
+      </c>
+      <c r="E25">
+        <f>D25 * $A$28 * ( 1 / Metingen!F25+ 1 / Metingen!G25)</f>
+        <v>5.9713338004074585E-4</v>
+      </c>
+      <c r="F25">
+        <f>Metingen!E25 / Metingen!G25</f>
+        <v>0.50596658711217191</v>
+      </c>
+      <c r="G25">
+        <f>F25 * $A$28 * (1 / Metingen!E25 + 1 / Metingen!G25)</f>
+        <v>5.9903205533499277E-4</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="0"/>
+        <v>0.78420484484214981</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="1"/>
+        <v>5.9713508069160514E-4</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="2"/>
+        <v>0.77943143466855702</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="3"/>
+        <v>5.9907471116685761E-4</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="4"/>
+        <v>2.3867050867963924E-3</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="5"/>
+        <v>1.1962097918584626E-3</v>
+      </c>
+      <c r="N25">
+        <f>Metingen!C25/$A$4</f>
+        <v>0.46948356807511737</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="6"/>
+        <v>0.37976181832655637</v>
+      </c>
+      <c r="P25">
+        <v>1E-3</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="7"/>
+        <v>3.1423710489295029E-2</v>
+      </c>
+      <c r="R25">
+        <f t="shared" si="8"/>
+        <v>1.5989338590458556E-2</v>
+      </c>
+      <c r="S25">
+        <f t="shared" si="9"/>
+        <v>0.50883038131049385</v>
+      </c>
+      <c r="T25">
+        <f t="shared" si="10"/>
+        <v>50.883038131049382</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A26" s="6"/>
+      <c r="C26" s="4">
+        <v>5</v>
+      </c>
+      <c r="D26">
+        <f>Metingen!F26 / Metingen!G26</f>
+        <v>0.4948289578361178</v>
+      </c>
+      <c r="E26">
+        <f>D26 * $A$28 * ( 1 / Metingen!F26+ 1 / Metingen!G26)</f>
+        <v>5.9460181298174935E-4</v>
+      </c>
+      <c r="F26">
+        <f>Metingen!E26 / Metingen!G26</f>
+        <v>0.49920445505171041</v>
+      </c>
+      <c r="G26">
+        <f>F26 * $A$28 * (1 / Metingen!E26 + 1 / Metingen!G26)</f>
+        <v>5.9634226533480928E-4</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="0"/>
+        <v>0.79056929774709928</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="1"/>
+        <v>5.9463361445377292E-4</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="2"/>
+        <v>0.78619370868140082</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="3"/>
+        <v>5.9634302017645983E-4</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="4"/>
+        <v>2.1877945328492299E-3</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="5"/>
+        <v>1.1909766346302328E-3</v>
+      </c>
+      <c r="N26">
+        <f>Metingen!C26/$A$4</f>
+        <v>0.3129890453834116</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="6"/>
+        <v>0.25317454555103758</v>
+      </c>
+      <c r="P26">
+        <v>1E-3</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="7"/>
+        <v>4.3207237285396674E-2</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="8"/>
+        <v>2.3907558560375127E-2</v>
+      </c>
+      <c r="S26">
+        <f t="shared" si="9"/>
+        <v>0.55332300934814649</v>
+      </c>
+      <c r="T26">
+        <f t="shared" si="10"/>
+        <v>55.332300934814647</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A27" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W27" s="9"/>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A28" s="8">
+        <v>1E-3</v>
+      </c>
+      <c r="W28" s="9"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A29" s="8"/>
+      <c r="W29" s="9"/>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A30" s="8"/>
+      <c r="W30" s="9"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A31" s="8"/>
+      <c r="W31" s="9"/>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A32" s="8"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Data/Data-sheet.xlsx
+++ b/Data/Data-sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tristancools/Documents/Arduino/Project-experimenteren2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{574319FD-C77A-C747-B259-37068857164B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D504D27-61F0-5A4F-A6EB-ABD0E63ADA92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Kalibratie" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="55">
   <si>
     <t>d(cm)</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>Foutpercentage</t>
+  </si>
+  <si>
+    <t>AF (dtheta)</t>
   </si>
 </sst>
 </file>
@@ -4145,13 +4148,14 @@
     <col min="9" max="9" width="8.33203125" customWidth="1"/>
     <col min="10" max="10" width="8" customWidth="1"/>
     <col min="11" max="11" width="7.83203125" customWidth="1"/>
-    <col min="12" max="13" width="8.33203125" customWidth="1"/>
+    <col min="12" max="12" width="8.33203125" customWidth="1"/>
+    <col min="13" max="13" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19.5" customWidth="1"/>
-    <col min="15" max="16" width="16.6640625" customWidth="1"/>
-    <col min="17" max="17" width="19" customWidth="1"/>
-    <col min="18" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="17.6640625" customWidth="1"/>
-    <col min="20" max="20" width="20.1640625" customWidth="1"/>
+    <col min="15" max="15" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="18" customWidth="1"/>
     <col min="22" max="22" width="17.6640625" customWidth="1"/>
   </cols>
@@ -4192,7 +4196,7 @@
         <v>45</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>22</v>
